--- a/business-libraries/test-data/class_system/assessment.xlsx
+++ b/business-libraries/test-data/class_system/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:Q3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,102 +419,51 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>结果可见性*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>来源属性*</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>手册出处*</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>版本*</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
-      </c>
-      <c r="R1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="S1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="T1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="V1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="X1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AA1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>后续建议动作</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B2" t="str">
-        <v>班级系统建设班级氛围五问</v>
+        <v>班级五系统速评</v>
       </c>
       <c r="C2" t="str">
-        <v>班级氛围</v>
+        <v>五系统速评</v>
       </c>
       <c r="D2" t="str">
         <v>class_system</v>
@@ -523,102 +472,51 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H2" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I2" t="str">
-        <v>self_report</v>
+        <v>monthly</v>
       </c>
       <c r="J2" t="str">
-        <v>manual</v>
+        <v>是</v>
       </c>
       <c r="K2" t="str">
-        <v>monthly</v>
+        <v>5</v>
       </c>
       <c r="L2" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M2" t="str">
-        <v>3</v>
+        <v>sensitive</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O2" t="str">
-        <v>5</v>
+        <v>班级系统建设手册v1</v>
       </c>
       <c r="P2" t="str">
-        <v>每月一次</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>30</v>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U2" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V2" t="str">
-        <v>highly_sensitive</v>
-      </c>
-      <c r="W2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v>技术理论手册V5 第3章</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>回顾最近一周状态，产出多维评估结果</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>全国中小学班主任常模 N=3200</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>Cronbach α=0.87</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>与GHQ-12 相关系数 r=0.64</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>数据仅用于教学支持，不用于人事考核</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>适用于在职班主任，不适用于实习或代课教师</v>
-      </c>
-      <c r="AG2" t="str">
-        <v>教师正在经历重大个人变故时，建议先转介心理支持再施测</v>
-      </c>
-      <c r="AH2" t="str">
-        <v>如总分&gt;=17，建议进行深度访谈并启动个案</v>
+        <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C_QUICK</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="B3" t="str">
-        <v>班级系统建设班级管理效能评估</v>
+        <v>班级能量场问卷</v>
       </c>
       <c r="C3" t="str">
-        <v>管理效能</v>
+        <v>能量场</v>
       </c>
       <c r="D3" t="str">
         <v>class_system</v>
@@ -627,103 +525,52 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>4</v>
       </c>
       <c r="L3" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M3" t="str">
-        <v>5</v>
+        <v>sensitive</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O3" t="str">
-        <v>8</v>
+        <v>班级系统建设手册v1</v>
       </c>
       <c r="P3" t="str">
-        <v>学期初/学期末</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q3" t="str">
-        <v>90</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U3" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V3" t="str">
-        <v>internal</v>
-      </c>
-      <c r="W3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v>技术理论手册V5 第4章</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>评估教师在班级系统建设相关维度的资源与压力状况</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>全国中小学班主任常模 N=2800</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>Cronbach α=0.82</v>
-      </c>
-      <c r="AD3" t="str">
-        <v>内容效度经专家评审</v>
-      </c>
-      <c r="AE3" t="str">
-        <v>数据仅用于教学支持</v>
-      </c>
-      <c r="AF3" t="str">
-        <v>适用于在职班主任</v>
-      </c>
-      <c r="AG3" t="str">
-        <v>教师在严重心理危机时，建议先进行心理评估</v>
-      </c>
-      <c r="AH3" t="str">
-        <v>根据评估结果推荐相应的支持工具</v>
+        <v>教师端观察问卷，与五系统速评交叉验证，用于判断班级氛围的稳定性。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:J22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -739,552 +586,706 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B2" t="str">
-        <v>q1</v>
+        <v>goal1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>COHESION</v>
+        <v>目标系统</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>学生清楚本班共同目标以及为什么要实现它。</v>
       </c>
       <c r="F2" t="str">
-        <v>这一周，我有多少时间感到班级成员间的凝聚与归属感？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H2" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B3" t="str">
-        <v>q2</v>
+        <v>goal2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>DISCIPLINE</v>
+        <v>目标系统</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>班级目标已转化为本学期可观察的里程碑。</v>
       </c>
       <c r="F3" t="str">
-        <v>这一周，我有多少时间感到课堂纪律状况？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H3" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B4" t="str">
-        <v>q3</v>
+        <v>goal3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>ENGAGEMENT</v>
+        <v>目标系统</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>日常活动和评价与班级目标保持一致。</v>
       </c>
       <c r="F4" t="str">
-        <v>这一周，我有多少时间感到学生对班级活动的参与积极性？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H4" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B5" t="str">
-        <v>q4</v>
+        <v>org1</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>CONFLICT</v>
+        <v>组织系统</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>班干部岗位职责清楚且能稳定运转。</v>
       </c>
       <c r="F5" t="str">
-        <v>这一周，我有多少时间感到班级内冲突频率和处理效果？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H5" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B6" t="str">
-        <v>q5</v>
+        <v>org2</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>CLIMATE</v>
+        <v>组织系统</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>班级事务能够由学生参与分工，而非全部由教师承担。</v>
       </c>
       <c r="F6" t="str">
-        <v>这一周，我有多少时间感到班级整体心理安全感？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H6" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>C_QUICK</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B7" t="str">
-        <v>q1</v>
+        <v>org3</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>COHESION</v>
+        <v>组织系统</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>班级日常关键节点有明确的执行流程。</v>
       </c>
       <c r="F7" t="str">
-        <v>在班级系统建设方面，评估班级成员间的凝聚与归属感的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H7" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>C_QUICK</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B8" t="str">
-        <v>q2</v>
+        <v>act1</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>DISCIPLINE</v>
+        <v>活动系统</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>班级活动能够回应学生真实需要。</v>
       </c>
       <c r="F8" t="str">
-        <v>在班级系统建设方面，评估课堂纪律状况的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H8" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>C_QUICK</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B9" t="str">
-        <v>q3</v>
+        <v>act2</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>ENGAGEMENT</v>
+        <v>活动系统</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>活动结束后会进行简短复盘并形成改进。</v>
       </c>
       <c r="F9" t="str">
-        <v>在班级系统建设方面，评估学生对班级活动的参与积极性的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H9" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>C_QUICK</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B10" t="str">
-        <v>q4</v>
+        <v>act3</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>CONFLICT</v>
+        <v>活动系统</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>多数学生都有参与和承担责任的机会。</v>
       </c>
       <c r="F10" t="str">
-        <v>在班级系统建设方面，评估班级内冲突频率和处理效果的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H10" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>C_QUICK</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B11" t="str">
-        <v>q5</v>
+        <v>env1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>CLIMATE</v>
+        <v>环境系统</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>班级空间和信息布置能够支持秩序与学习。</v>
       </c>
       <c r="F11" t="str">
-        <v>在班级系统建设方面，评估班级整体心理安全感的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H11" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v>5</v>
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="B12" t="str">
+        <v>env2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>single</v>
+      </c>
+      <c r="D12" t="str">
+        <v>环境系统</v>
+      </c>
+      <c r="E12" t="str">
+        <v>班级规则由师生共同理解而非只贴在墙上。</v>
+      </c>
+      <c r="F12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G12" t="str">
+        <v>是</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>是</v>
+      </c>
+      <c r="J12" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="B13" t="str">
+        <v>env3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>single</v>
+      </c>
+      <c r="D13" t="str">
+        <v>环境系统</v>
+      </c>
+      <c r="E13" t="str">
+        <v>出现混乱时能够快速恢复稳定节奏。</v>
+      </c>
+      <c r="F13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G13" t="str">
+        <v>是</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <v>是</v>
+      </c>
+      <c r="J13" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="B14" t="str">
+        <v>rel1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>single</v>
+      </c>
+      <c r="D14" t="str">
+        <v>关系系统</v>
+      </c>
+      <c r="E14" t="str">
+        <v>学生普遍感到被尊重、被听见。</v>
+      </c>
+      <c r="F14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G14" t="str">
+        <v>是</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
+        <v>是</v>
+      </c>
+      <c r="J14" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="B15" t="str">
+        <v>rel2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>single</v>
+      </c>
+      <c r="D15" t="str">
+        <v>关系系统</v>
+      </c>
+      <c r="E15" t="str">
+        <v>学生冲突能够被及时处理并修复关系。</v>
+      </c>
+      <c r="F15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G15" t="str">
+        <v>是</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <v>是</v>
+      </c>
+      <c r="J15" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="B16" t="str">
+        <v>rel3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>single</v>
+      </c>
+      <c r="D16" t="str">
+        <v>关系系统</v>
+      </c>
+      <c r="E16" t="str">
+        <v>班级中存在稳定的互助和同伴支持。</v>
+      </c>
+      <c r="F16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G16" t="str">
+        <v>是</v>
+      </c>
+      <c r="H16" t="str">
+        <v>1</v>
+      </c>
+      <c r="I16" t="str">
+        <v>是</v>
+      </c>
+      <c r="J16" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="B17" t="str">
+        <v>en1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>single</v>
+      </c>
+      <c r="D17" t="str">
+        <v>秩序能量</v>
+      </c>
+      <c r="E17" t="str">
+        <v>我不在教室时，班级秩序仍能维持。</v>
+      </c>
+      <c r="F17" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G17" t="str">
+        <v>是</v>
+      </c>
+      <c r="H17" t="str">
+        <v>1</v>
+      </c>
+      <c r="I17" t="str">
+        <v>是</v>
+      </c>
+      <c r="J17" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="B18" t="str">
+        <v>en2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>single</v>
+      </c>
+      <c r="D18" t="str">
+        <v>秩序能量</v>
+      </c>
+      <c r="E18" t="str">
+        <v>课间到上课的过渡不需要我反复提醒。</v>
+      </c>
+      <c r="F18" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G18" t="str">
+        <v>是</v>
+      </c>
+      <c r="H18" t="str">
+        <v>1</v>
+      </c>
+      <c r="I18" t="str">
+        <v>是</v>
+      </c>
+      <c r="J18" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="B19" t="str">
+        <v>en3</v>
+      </c>
+      <c r="C19" t="str">
+        <v>single</v>
+      </c>
+      <c r="D19" t="str">
+        <v>学习能量</v>
+      </c>
+      <c r="E19" t="str">
+        <v>多数学生在自习时能自主投入。</v>
+      </c>
+      <c r="F19" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G19" t="str">
+        <v>是</v>
+      </c>
+      <c r="H19" t="str">
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
+        <v>是</v>
+      </c>
+      <c r="J19" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="B20" t="str">
+        <v>en4</v>
+      </c>
+      <c r="C20" t="str">
+        <v>single</v>
+      </c>
+      <c r="D20" t="str">
+        <v>学习能量</v>
+      </c>
+      <c r="E20" t="str">
+        <v>学生会主动追问自己不懂的问题。</v>
+      </c>
+      <c r="F20" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G20" t="str">
+        <v>是</v>
+      </c>
+      <c r="H20" t="str">
+        <v>1</v>
+      </c>
+      <c r="I20" t="str">
+        <v>是</v>
+      </c>
+      <c r="J20" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="B21" t="str">
+        <v>en5</v>
+      </c>
+      <c r="C21" t="str">
+        <v>single</v>
+      </c>
+      <c r="D21" t="str">
+        <v>联结能量</v>
+      </c>
+      <c r="E21" t="str">
+        <v>学生之间会自发互相帮助。</v>
+      </c>
+      <c r="F21" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G21" t="str">
+        <v>是</v>
+      </c>
+      <c r="H21" t="str">
+        <v>1</v>
+      </c>
+      <c r="I21" t="str">
+        <v>是</v>
+      </c>
+      <c r="J21" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="B22" t="str">
+        <v>en6</v>
+      </c>
+      <c r="C22" t="str">
+        <v>single</v>
+      </c>
+      <c r="D22" t="str">
+        <v>联结能量</v>
+      </c>
+      <c r="E22" t="str">
+        <v>新转入的学生能较快融入集体。</v>
+      </c>
+      <c r="F22" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G22" t="str">
+        <v>是</v>
+      </c>
+      <c r="H22" t="str">
+        <v>1</v>
+      </c>
+      <c r="I22" t="str">
+        <v>是</v>
+      </c>
+      <c r="J22" t="str">
+        <v>compute</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1370,16 +1371,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:I9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1409,25 +1480,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B2" t="str">
-        <v>COHESION</v>
+        <v>CS_GOAL</v>
       </c>
       <c r="C2" t="str">
-        <v>班级凝聚力</v>
+        <v>目标系统</v>
       </c>
       <c r="D2" t="str">
-        <v>q1</v>
+        <v>goal1,goal2,goal3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1436,33 +1501,27 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>评估班级成员间的凝聚与归属感</v>
+        <v>目标系统维度</v>
       </c>
       <c r="H2" t="str">
-        <v>&gt;=4 分：凝聚力强</v>
+        <v>目标未被学生理解或未转化为可观察里程碑</v>
       </c>
       <c r="I2" t="str">
-        <v>&lt;=2 分：凝聚力不足</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K2" t="str">
-        <v>0.9</v>
+        <v>目标清晰且已落地</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B3" t="str">
-        <v>DISCIPLINE</v>
+        <v>CS_ORG</v>
       </c>
       <c r="C3" t="str">
-        <v>课堂纪律</v>
+        <v>组织系统</v>
       </c>
       <c r="D3" t="str">
-        <v>q2</v>
+        <v>org1,org2,org3</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1471,33 +1530,27 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>评估课堂纪律状况</v>
+        <v>组织系统维度</v>
       </c>
       <c r="H3" t="str">
-        <v>&gt;=4 分：纪律良好</v>
+        <v>岗位职责不清，事务集中在教师身上</v>
       </c>
       <c r="I3" t="str">
-        <v>&lt;=2 分：纪律松散</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2.6</v>
-      </c>
-      <c r="K3" t="str">
-        <v>1.0</v>
+        <v>学生分工稳定运转</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B4" t="str">
-        <v>ENGAGEMENT</v>
+        <v>CS_ACTIVITY</v>
       </c>
       <c r="C4" t="str">
-        <v>学生参与度</v>
+        <v>活动系统</v>
       </c>
       <c r="D4" t="str">
-        <v>q3</v>
+        <v>act1,act2,act3</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1506,33 +1559,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>评估学生对班级活动的参与积极性</v>
+        <v>活动系统维度</v>
       </c>
       <c r="H4" t="str">
-        <v>&gt;=4 分：参与积极</v>
+        <v>活动脱离学生真实需要且缺少复盘</v>
       </c>
       <c r="I4" t="str">
-        <v>&lt;=2 分：参与度低</v>
-      </c>
-      <c r="J4" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0.85</v>
+        <v>活动有回应、有复盘</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B5" t="str">
-        <v>CONFLICT</v>
+        <v>CS_ENV</v>
       </c>
       <c r="C5" t="str">
-        <v>冲突管理</v>
+        <v>环境系统</v>
       </c>
       <c r="D5" t="str">
-        <v>q4</v>
+        <v>env1,env2,env3</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1541,33 +1588,27 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>评估班级内冲突频率和处理效果</v>
+        <v>环境系统维度</v>
       </c>
       <c r="H5" t="str">
-        <v>&gt;=4 分：冲突管理得当</v>
+        <v>规则停留在墙上，混乱后难以恢复</v>
       </c>
       <c r="I5" t="str">
-        <v>&lt;=2 分：冲突频发</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2.4</v>
-      </c>
-      <c r="K5" t="str">
-        <v>0.95</v>
+        <v>环境与规则支持秩序</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="B6" t="str">
-        <v>CLIMATE</v>
+        <v>CS_RELATION</v>
       </c>
       <c r="C6" t="str">
-        <v>班级氛围</v>
+        <v>关系系统</v>
       </c>
       <c r="D6" t="str">
-        <v>q5</v>
+        <v>rel1,rel2,rel3</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1576,33 +1617,27 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>评估班级整体心理安全感</v>
+        <v>关系系统维度</v>
       </c>
       <c r="H6" t="str">
-        <v>&gt;=4 分：氛围健康</v>
+        <v>冲突难以修复，缺少同伴互助</v>
       </c>
       <c r="I6" t="str">
-        <v>&lt;=2 分：氛围压抑</v>
-      </c>
-      <c r="J6" t="str">
-        <v>3.1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>0.8</v>
+        <v>关系稳定，学生被听见</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>C_QUICK</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="B7" t="str">
-        <v>COHESION</v>
+        <v>CS_ORDER</v>
       </c>
       <c r="C7" t="str">
-        <v>班级凝聚力</v>
+        <v>秩序能量</v>
       </c>
       <c r="D7" t="str">
-        <v>q1</v>
+        <v>en1,en2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1611,33 +1646,27 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>评估班级成员间的凝聚与归属感</v>
+        <v>秩序能量维度</v>
       </c>
       <c r="H7" t="str">
-        <v>&gt;=4 分：凝聚力强</v>
+        <v>秩序需要教师持续在场维持</v>
       </c>
       <c r="I7" t="str">
-        <v>&lt;=2 分：凝聚力不足</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K7" t="str">
-        <v>0.9</v>
+        <v>秩序可自主维持</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>C_QUICK</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="B8" t="str">
-        <v>DISCIPLINE</v>
+        <v>CS_LEARNING</v>
       </c>
       <c r="C8" t="str">
-        <v>课堂纪律</v>
+        <v>学习能量</v>
       </c>
       <c r="D8" t="str">
-        <v>q2</v>
+        <v>en3,en4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -1646,33 +1675,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>评估课堂纪律状况</v>
+        <v>学习能量维度</v>
       </c>
       <c r="H8" t="str">
-        <v>&gt;=4 分：纪律良好</v>
+        <v>学习投入依赖外部推动</v>
       </c>
       <c r="I8" t="str">
-        <v>&lt;=2 分：纪律松散</v>
-      </c>
-      <c r="J8" t="str">
-        <v>2.6</v>
-      </c>
-      <c r="K8" t="str">
-        <v>1.0</v>
+        <v>学习氛围自发</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>C_QUICK</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="B9" t="str">
-        <v>ENGAGEMENT</v>
+        <v>CS_CONNECT</v>
       </c>
       <c r="C9" t="str">
-        <v>学生参与度</v>
+        <v>联结能量</v>
       </c>
       <c r="D9" t="str">
-        <v>q3</v>
+        <v>en5,en6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -1681,94 +1704,18 @@
         <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v>评估学生对班级活动的参与积极性</v>
+        <v>联结能量维度</v>
       </c>
       <c r="H9" t="str">
-        <v>&gt;=4 分：参与积极</v>
+        <v>学生之间缺少正向联结</v>
       </c>
       <c r="I9" t="str">
-        <v>&lt;=2 分：参与度低</v>
-      </c>
-      <c r="J9" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K9" t="str">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>C_QUICK</v>
-      </c>
-      <c r="B10" t="str">
-        <v>CONFLICT</v>
-      </c>
-      <c r="C10" t="str">
-        <v>冲突管理</v>
-      </c>
-      <c r="D10" t="str">
-        <v>q4</v>
-      </c>
-      <c r="E10" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F10" t="str">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
-        <v>评估班级内冲突频率和处理效果</v>
-      </c>
-      <c r="H10" t="str">
-        <v>&gt;=4 分：冲突管理得当</v>
-      </c>
-      <c r="I10" t="str">
-        <v>&lt;=2 分：冲突频发</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2.4</v>
-      </c>
-      <c r="K10" t="str">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>C_QUICK</v>
-      </c>
-      <c r="B11" t="str">
-        <v>CLIMATE</v>
-      </c>
-      <c r="C11" t="str">
-        <v>班级氛围</v>
-      </c>
-      <c r="D11" t="str">
-        <v>q5</v>
-      </c>
-      <c r="E11" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F11" t="str">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
-        <v>评估班级整体心理安全感</v>
-      </c>
-      <c r="H11" t="str">
-        <v>&gt;=4 分：氛围健康</v>
-      </c>
-      <c r="I11" t="str">
-        <v>&lt;=2 分：氛围压抑</v>
-      </c>
-      <c r="J11" t="str">
-        <v>3.1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>0.8</v>
+        <v>同伴联结紧密</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/assessment.xlsx
+++ b/business-libraries/test-data/class_system/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,21 +437,36 @@
         <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
+        <v>量表角色*</v>
+      </c>
+      <c r="M1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="O1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="P1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="Q1" t="str">
         <v>结果可见性*</v>
       </c>
-      <c r="M1" t="str">
+      <c r="R1" t="str">
         <v>数据敏感级*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="S1" t="str">
         <v>来源属性*</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
         <v>版本*</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="V1" t="str">
         <v>量表说明</v>
       </c>
     </row>
@@ -490,21 +505,36 @@
         <v>5</v>
       </c>
       <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M2" t="str">
+      <c r="R2" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N2" t="str">
+      <c r="S2" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O2" t="str">
+      <c r="T2" t="str">
         <v>班级系统建设手册v1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="U2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="V2" t="str">
         <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
       </c>
     </row>
@@ -543,27 +573,42 @@
         <v>4</v>
       </c>
       <c r="L3" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="M3" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>量表[CS_FIVE_SYS].均分 &gt;= 3.2 或 量表[CS_FIVE_SYS].维度[CS_RELATION] &gt;= 3.5</v>
+      </c>
+      <c r="P3" t="str">
+        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
+      </c>
+      <c r="Q3" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M3" t="str">
+      <c r="R3" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N3" t="str">
+      <c r="S3" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O3" t="str">
+      <c r="T3" t="str">
         <v>班级系统建设手册v1</v>
       </c>
-      <c r="P3" t="str">
+      <c r="U3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="V3" t="str">
         <v>教师端观察问卷，与五系统速评交叉验证，用于判断班级氛围的稳定性。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/class_system/assessment.xlsx
+++ b/business-libraries/test-data/class_system/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,55 +419,103 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
@@ -487,55 +535,103 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>monthly</v>
       </c>
-      <c r="J2" t="str">
-        <v>是</v>
-      </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
+        <v>是</v>
+      </c>
+      <c r="M2" t="str">
         <v>5</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
+      <c r="AL2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>4</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[CS_FIVE_SYS].均分 &gt;= 3.2 或 量表[CS_FIVE_SYS].维度[CS_RELATION] &gt;= 3.5</v>
+      </c>
+      <c r="U3" t="str">
+        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>教师端观察问卷，与五系统速评交叉验证，用于判断班级氛围的稳定性。</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>CS_FIVE_SYS</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[CS_FIVE_SYS].均分 &gt;= 3.2 或 量表[CS_FIVE_SYS].维度[CS_RELATION] &gt;= 3.5</v>
-      </c>
-      <c r="P3" t="str">
-        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T3" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>教师端观察问卷，与五系统速评交叉验证，用于判断班级氛围的稳定性。</v>
+      <c r="AL3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:P22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,22 +775,40 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
@@ -663,22 +825,40 @@
         <v>目标系统</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>学生清楚本班共同目标以及为什么要实现它。</v>
       </c>
-      <c r="F2" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G2" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I2" t="str">
         <v>是</v>
       </c>
       <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>是</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -695,22 +875,40 @@
         <v>目标系统</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>班级目标已转化为本学期可观察的里程碑。</v>
       </c>
-      <c r="F3" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G3" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I3" t="str">
         <v>是</v>
       </c>
       <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>是</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -727,22 +925,40 @@
         <v>目标系统</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>日常活动和评价与班级目标保持一致。</v>
       </c>
-      <c r="F4" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G4" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>是</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -759,22 +975,40 @@
         <v>组织系统</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>班干部岗位职责清楚且能稳定运转。</v>
       </c>
-      <c r="F5" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G5" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I5" t="str">
         <v>是</v>
       </c>
       <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>是</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -791,22 +1025,40 @@
         <v>组织系统</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>班级事务能够由学生参与分工，而非全部由教师承担。</v>
       </c>
-      <c r="F6" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G6" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I6" t="str">
         <v>是</v>
       </c>
       <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>是</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -823,22 +1075,40 @@
         <v>组织系统</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>班级日常关键节点有明确的执行流程。</v>
       </c>
-      <c r="F7" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G7" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I7" t="str">
         <v>是</v>
       </c>
       <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>是</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -855,22 +1125,40 @@
         <v>活动系统</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>班级活动能够回应学生真实需要。</v>
       </c>
-      <c r="F8" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G8" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I8" t="str">
         <v>是</v>
       </c>
       <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>是</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -887,22 +1175,40 @@
         <v>活动系统</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>活动结束后会进行简短复盘并形成改进。</v>
       </c>
-      <c r="F9" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G9" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>是</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -919,22 +1225,40 @@
         <v>活动系统</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>多数学生都有参与和承担责任的机会。</v>
       </c>
-      <c r="F10" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G10" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I10" t="str">
         <v>是</v>
       </c>
       <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>是</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -951,22 +1275,40 @@
         <v>环境系统</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>班级空间和信息布置能够支持秩序与学习。</v>
       </c>
-      <c r="F11" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G11" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I11" t="str">
         <v>是</v>
       </c>
       <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>是</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -983,22 +1325,40 @@
         <v>环境系统</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>班级规则由师生共同理解而非只贴在墙上。</v>
       </c>
-      <c r="F12" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G12" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I12" t="str">
         <v>是</v>
       </c>
       <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>是</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1015,22 +1375,40 @@
         <v>环境系统</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>出现混乱时能够快速恢复稳定节奏。</v>
       </c>
-      <c r="F13" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G13" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I13" t="str">
         <v>是</v>
       </c>
       <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>是</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1047,22 +1425,40 @@
         <v>关系系统</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>学生普遍感到被尊重、被听见。</v>
       </c>
-      <c r="F14" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G14" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I14" t="str">
         <v>是</v>
       </c>
       <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>是</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1079,22 +1475,40 @@
         <v>关系系统</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>学生冲突能够被及时处理并修复关系。</v>
       </c>
-      <c r="F15" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G15" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I15" t="str">
         <v>是</v>
       </c>
       <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>是</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1111,22 +1525,40 @@
         <v>关系系统</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>班级中存在稳定的互助和同伴支持。</v>
       </c>
-      <c r="F16" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G16" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I16" t="str">
         <v>是</v>
       </c>
       <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>是</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1143,22 +1575,40 @@
         <v>秩序能量</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>我不在教室时，班级秩序仍能维持。</v>
       </c>
-      <c r="F17" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G17" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I17" t="str">
         <v>是</v>
       </c>
       <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>是</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1175,22 +1625,40 @@
         <v>秩序能量</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>课间到上课的过渡不需要我反复提醒。</v>
       </c>
-      <c r="F18" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G18" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I18" t="str">
         <v>是</v>
       </c>
       <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>是</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1207,22 +1675,40 @@
         <v>学习能量</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>多数学生在自习时能自主投入。</v>
       </c>
-      <c r="F19" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G19" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I19" t="str">
         <v>是</v>
       </c>
       <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>是</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1239,22 +1725,40 @@
         <v>学习能量</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>学生会主动追问自己不懂的问题。</v>
       </c>
-      <c r="F20" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G20" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I20" t="str">
         <v>是</v>
       </c>
       <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>是</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1271,22 +1775,40 @@
         <v>联结能量</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>学生之间会自发互相帮助。</v>
       </c>
-      <c r="F21" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G21" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I21" t="str">
         <v>是</v>
       </c>
       <c r="J21" t="str">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>是</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>compute</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1303,27 +1825,45 @@
         <v>联结能量</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>新转入的学生能较快融入集体。</v>
       </c>
-      <c r="F22" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G22" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I22" t="str">
         <v>是</v>
       </c>
       <c r="J22" t="str">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>是</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>compute</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P22"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1495,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1525,6 +2065,12 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1554,6 +2100,12 @@
       <c r="I2" t="str">
         <v>目标清晰且已落地</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1583,6 +2135,12 @@
       <c r="I3" t="str">
         <v>学生分工稳定运转</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1612,6 +2170,12 @@
       <c r="I4" t="str">
         <v>活动有回应、有复盘</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1641,6 +2205,12 @@
       <c r="I5" t="str">
         <v>环境与规则支持秩序</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1670,6 +2240,12 @@
       <c r="I6" t="str">
         <v>关系稳定，学生被听见</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1699,6 +2275,12 @@
       <c r="I7" t="str">
         <v>秩序可自主维持</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1728,6 +2310,12 @@
       <c r="I8" t="str">
         <v>学习氛围自发</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1757,10 +2345,16 @@
       <c r="I9" t="str">
         <v>同伴联结紧密</v>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/assessment.xlsx
+++ b/business-libraries/test-data/class_system/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,7 +520,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B2" t="str">
         <v>班级五系统速评</v>
@@ -586,7 +586,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W2" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X2" t="str">
         <v>sensitive</v>
@@ -601,7 +601,7 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AB2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC2" t="str">
         <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
@@ -631,12 +631,12 @@
         <v>入口筛查</v>
       </c>
       <c r="AL2" t="str">
-        <v/>
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B3" t="str">
         <v>班级能量场问卷</v>
@@ -687,13 +687,13 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="S3" t="str">
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[CS_FIVE_SYS].均分 &gt;= 3.2 或 量表[CS_FIVE_SYS].维度[CS_RELATION] &gt;= 3.5</v>
+        <v>量表[CS_S1].均分 &gt;= 3.2 或 量表[CS_S1].维度[CS_S1D5] &gt;= 3.5</v>
       </c>
       <c r="U3" t="str">
         <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
@@ -702,7 +702,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W3" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X3" t="str">
         <v>sensitive</v>
@@ -717,10 +717,10 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AB3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>教师端观察问卷，与五系统速评交叉验证，用于判断班级氛围的稳定性。</v>
+        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -747,19 +747,251 @@
         <v>深度诊断</v>
       </c>
       <c r="AL3" t="str">
-        <v/>
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>堰塞湖四信号自查</v>
+      </c>
+      <c r="C4" t="str">
+        <v>堰塞湖自查</v>
+      </c>
+      <c r="D4" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E4" t="str">
+        <v>all</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I4" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J4" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K4" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L4" t="str">
+        <v>否</v>
+      </c>
+      <c r="M4" t="str">
+        <v>3</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>量表[CS_S1].均分 &gt;= 3.2</v>
+      </c>
+      <c r="U4" t="str">
+        <v>五系统速评均分 ≥ 3.2 时建议做一次堰塞湖自查，排查班级是否有被截断的信号</v>
+      </c>
+      <c r="V4" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W4" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X4" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>班级层面预警自查：情绪、冲突、需求、声音四类信号被截断时，问题会在水面下蓄积，最终以突发方式爆发。信号频率越高越需要及时疏解。</v>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+      <c r="AK4" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>大型活动组织专项评估</v>
+      </c>
+      <c r="C5" t="str">
+        <v>大型活动组织专项</v>
+      </c>
+      <c r="D5" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E5" t="str">
+        <v>all</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I5" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J5" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K5" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="L5" t="str">
+        <v>否</v>
+      </c>
+      <c r="M5" t="str">
+        <v>6</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v>量表[CS_S1].维度[CS_S1D2] &gt;= 3.2</v>
+      </c>
+      <c r="U5" t="str">
+        <v>权力系统维度偏高时才需要做大型活动专项评估</v>
+      </c>
+      <c r="V5" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W5" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X5" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>班级组织大型活动（运动会、汇演、外出实践等）前的专项评估。</v>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+      <c r="AK5" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -813,10 +1045,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>goal1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -863,10 +1095,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>goal2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -913,10 +1145,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>goal3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -963,16 +1195,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>org1</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -1013,16 +1245,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>org2</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -1063,16 +1295,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>org3</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -1113,16 +1345,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>act1</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1163,16 +1395,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>act2</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -1213,16 +1445,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>act3</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1263,16 +1495,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B11" t="str">
-        <v>env1</v>
+        <v>q10</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1313,16 +1545,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B12" t="str">
-        <v>env2</v>
+        <v>q11</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
       </c>
       <c r="D12" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -1363,16 +1595,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B13" t="str">
-        <v>env3</v>
+        <v>q12</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
       </c>
       <c r="D13" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -1413,10 +1645,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B14" t="str">
-        <v>rel1</v>
+        <v>q13</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1463,10 +1695,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B15" t="str">
-        <v>rel2</v>
+        <v>q14</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1513,10 +1745,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B16" t="str">
-        <v>rel3</v>
+        <v>q15</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1563,10 +1795,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B17" t="str">
-        <v>en1</v>
+        <v>q1</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1613,10 +1845,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B18" t="str">
-        <v>en2</v>
+        <v>q2</v>
       </c>
       <c r="C18" t="str">
         <v>single</v>
@@ -1663,10 +1895,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B19" t="str">
-        <v>en3</v>
+        <v>q3</v>
       </c>
       <c r="C19" t="str">
         <v>single</v>
@@ -1713,10 +1945,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B20" t="str">
-        <v>en4</v>
+        <v>q4</v>
       </c>
       <c r="C20" t="str">
         <v>single</v>
@@ -1763,10 +1995,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B21" t="str">
-        <v>en5</v>
+        <v>q5</v>
       </c>
       <c r="C21" t="str">
         <v>single</v>
@@ -1813,10 +2045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B22" t="str">
-        <v>en6</v>
+        <v>q6</v>
       </c>
       <c r="C22" t="str">
         <v>single</v>
@@ -1861,9 +2093,509 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B23" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>single</v>
+      </c>
+      <c r="D23" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>最近两周，班级里学生或家长的情绪被反复压制、没有表达出口的频率？</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I23" t="str">
+        <v>否</v>
+      </c>
+      <c r="J23" t="str">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>是</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C24" t="str">
+        <v>single</v>
+      </c>
+      <c r="D24" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>最近两周，班级冲突被掩盖或回避、没有正式解决路径的频率？</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I24" t="str">
+        <v>否</v>
+      </c>
+      <c r="J24" t="str">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>是</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B25" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C25" t="str">
+        <v>single</v>
+      </c>
+      <c r="D25" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>最近两周，学生或家长的真实需求提出后长期得不到回应的频率？</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I25" t="str">
+        <v>否</v>
+      </c>
+      <c r="J25" t="str">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>是</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B26" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C26" t="str">
+        <v>single</v>
+      </c>
+      <c r="D26" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>最近两周，班级里部分学生的声音完全听不到、被边缘化的频率？</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I26" t="str">
+        <v>否</v>
+      </c>
+      <c r="J26" t="str">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>是</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B27" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>single</v>
+      </c>
+      <c r="D27" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>活动目标在开始前已经明确传达给所有参与者。</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I27" t="str">
+        <v>否</v>
+      </c>
+      <c r="J27" t="str">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>是</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B28" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>single</v>
+      </c>
+      <c r="D28" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>各岗位分工在活动前已经落实到具体的人。</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I28" t="str">
+        <v>否</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>是</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B29" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C29" t="str">
+        <v>single</v>
+      </c>
+      <c r="D29" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>活动现场的秩序基本由既定规则维持。</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I29" t="str">
+        <v>否</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>是</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B30" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C30" t="str">
+        <v>single</v>
+      </c>
+      <c r="D30" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>参与者对活动流程的熟悉程度足够。</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I30" t="str">
+        <v>否</v>
+      </c>
+      <c r="J30" t="str">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>是</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B31" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C31" t="str">
+        <v>single</v>
+      </c>
+      <c r="D31" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>活动中的突发情况能在现场快速处理。</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I31" t="str">
+        <v>否</v>
+      </c>
+      <c r="J31" t="str">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>是</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B32" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C32" t="str">
+        <v>single</v>
+      </c>
+      <c r="D32" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>活动结束后有复盘和资料归档。</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I32" t="str">
+        <v>否</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>是</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1888,13 +2620,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1902,13 +2634,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1916,13 +2648,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1930,13 +2662,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1944,13 +2676,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
@@ -1958,13 +2690,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B7" t="str">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>完全不符合</v>
+        <v>几乎没有</v>
       </c>
       <c r="D7" t="str">
         <v>1</v>
@@ -1972,13 +2704,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B8" t="str">
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>比较不符合</v>
+        <v>很少</v>
       </c>
       <c r="D8" t="str">
         <v>2</v>
@@ -1986,13 +2718,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B9" t="str">
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>一般</v>
+        <v>有时</v>
       </c>
       <c r="D9" t="str">
         <v>3</v>
@@ -2000,13 +2732,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B10" t="str">
         <v>4</v>
       </c>
       <c r="C10" t="str">
-        <v>比较符合</v>
+        <v>经常</v>
       </c>
       <c r="D10" t="str">
         <v>4</v>
@@ -2014,13 +2746,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B11" t="str">
         <v>5</v>
       </c>
       <c r="C11" t="str">
-        <v>非常符合</v>
+        <v>几乎每天</v>
       </c>
       <c r="D11" t="str">
         <v>5</v>
@@ -2035,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2074,16 +2806,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>CS_GOAL</v>
+        <v>CS_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>目标系统</v>
       </c>
       <c r="D2" t="str">
-        <v>goal1,goal2,goal3</v>
+        <v>q1,q2,q3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -2109,16 +2841,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>CS_ORG</v>
+        <v>CS_S1D2</v>
       </c>
       <c r="C3" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="D3" t="str">
-        <v>org1,org2,org3</v>
+        <v>q4,q5,q6</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -2127,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>组织系统维度</v>
+        <v>权力系统维度</v>
       </c>
       <c r="H3" t="str">
         <v>岗位职责不清，事务集中在教师身上</v>
@@ -2144,16 +2876,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>CS_ACTIVITY</v>
+        <v>CS_S1D3</v>
       </c>
       <c r="C4" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="D4" t="str">
-        <v>act1,act2,act3</v>
+        <v>q7,q8,q9</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -2162,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>活动系统维度</v>
+        <v>情感系统维度</v>
       </c>
       <c r="H4" t="str">
         <v>活动脱离学生真实需要且缺少复盘</v>
@@ -2179,16 +2911,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>CS_ENV</v>
+        <v>CS_S1D4</v>
       </c>
       <c r="C5" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="D5" t="str">
-        <v>env1,env2,env3</v>
+        <v>q10,q11,q12</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -2197,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>环境系统维度</v>
+        <v>规范系统维度</v>
       </c>
       <c r="H5" t="str">
         <v>规则停留在墙上，混乱后难以恢复</v>
@@ -2214,16 +2946,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>CS_RELATION</v>
+        <v>CS_S1D5</v>
       </c>
       <c r="C6" t="str">
         <v>关系系统</v>
       </c>
       <c r="D6" t="str">
-        <v>rel1,rel2,rel3</v>
+        <v>q13,q14,q15</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -2249,16 +2981,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>CS_ORDER</v>
+        <v>CS_S2D1</v>
       </c>
       <c r="C7" t="str">
         <v>秩序能量</v>
       </c>
       <c r="D7" t="str">
-        <v>en1,en2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -2284,16 +3016,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>CS_LEARNING</v>
+        <v>CS_S2D2</v>
       </c>
       <c r="C8" t="str">
         <v>学习能量</v>
       </c>
       <c r="D8" t="str">
-        <v>en3,en4</v>
+        <v>q3,q4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -2319,16 +3051,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>CS_CONNECT</v>
+        <v>CS_S2D3</v>
       </c>
       <c r="C9" t="str">
         <v>联结能量</v>
       </c>
       <c r="D9" t="str">
-        <v>en5,en6</v>
+        <v>q5,q6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -2352,9 +3084,114 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B10" t="str">
+        <v>CS_S3D1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="D10" t="str">
+        <v>q1,q2,q3,q4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>四类截断信号的总体频率，越高越接近爆发临界</v>
+      </c>
+      <c r="H10" t="str">
+        <v>信号频繁被截断，堰塞湖蓄积风险高</v>
+      </c>
+      <c r="I10" t="str">
+        <v>信号有正常表达出口</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B11" t="str">
+        <v>CS_S4D1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="D11" t="str">
+        <v>q1,q2,q6</v>
+      </c>
+      <c r="E11" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>CS_S4D2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="D12" t="str">
+        <v>q3,q4,q5</v>
+      </c>
+      <c r="E12" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/assessment.xlsx
+++ b/business-libraries/test-data/class_system/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,60 +419,108 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B2" t="str">
         <v>班级五系统速评</v>
@@ -487,60 +535,108 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>monthly</v>
       </c>
-      <c r="J2" t="str">
-        <v>是</v>
-      </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
+        <v>是</v>
+      </c>
+      <c r="M2" t="str">
         <v>5</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
+      <c r="AL2" t="str">
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B3" t="str">
         <v>班级能量场问卷</v>
@@ -555,67 +651,347 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>4</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[CS_S1].均分 &gt;= 3.2 或 量表[CS_S1].维度[CS_S1D5] &gt;= 3.5</v>
+      </c>
+      <c r="U3" t="str">
+        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>CS_FIVE_SYS</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[CS_FIVE_SYS].均分 &gt;= 3.2 或 量表[CS_FIVE_SYS].维度[CS_RELATION] &gt;= 3.5</v>
-      </c>
-      <c r="P3" t="str">
-        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
-      </c>
-      <c r="Q3" t="str">
+      <c r="AL3" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>堰塞湖四信号自查</v>
+      </c>
+      <c r="C4" t="str">
+        <v>堰塞湖自查</v>
+      </c>
+      <c r="D4" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E4" t="str">
+        <v>all</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I4" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J4" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K4" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L4" t="str">
+        <v>否</v>
+      </c>
+      <c r="M4" t="str">
+        <v>3</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>量表[CS_S1].均分 &gt;= 3.2</v>
+      </c>
+      <c r="U4" t="str">
+        <v>五系统速评均分 ≥ 3.2 时建议做一次堰塞湖自查，排查班级是否有被截断的信号</v>
+      </c>
+      <c r="V4" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="R3" t="str">
+      <c r="W4" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X4" t="str">
         <v>sensitive</v>
       </c>
-      <c r="S3" t="str">
+      <c r="Y4" t="str">
         <v>proprietary</v>
       </c>
-      <c r="T3" t="str">
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
         <v>班级系统建设手册v1</v>
       </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>教师端观察问卷，与五系统速评交叉验证，用于判断班级氛围的稳定性。</v>
+      <c r="AB4" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>班级层面预警自查：情绪、冲突、需求、声音四类信号被截断时，问题会在水面下蓄积，最终以突发方式爆发。信号频率越高越需要及时疏解。</v>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+      <c r="AK4" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>大型活动组织专项评估</v>
+      </c>
+      <c r="C5" t="str">
+        <v>大型活动组织专项</v>
+      </c>
+      <c r="D5" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E5" t="str">
+        <v>all</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I5" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J5" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K5" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="L5" t="str">
+        <v>否</v>
+      </c>
+      <c r="M5" t="str">
+        <v>6</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v>量表[CS_S1].维度[CS_S1D2] &gt;= 3.2</v>
+      </c>
+      <c r="U5" t="str">
+        <v>权力系统维度偏高时才需要做大型活动专项评估</v>
+      </c>
+      <c r="V5" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W5" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X5" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>班级组织大型活动（运动会、汇演、外出实践等）前的专项评估。</v>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+      <c r="AK5" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:P32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,30 +1007,48 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>goal1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -663,30 +1057,48 @@
         <v>目标系统</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>学生清楚本班共同目标以及为什么要实现它。</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G2" t="str">
-        <v>是</v>
-      </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
       <c r="I2" t="str">
         <v>是</v>
       </c>
       <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>是</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>goal2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -695,30 +1107,48 @@
         <v>目标系统</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>班级目标已转化为本学期可观察的里程碑。</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G3" t="str">
-        <v>是</v>
-      </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
       <c r="I3" t="str">
         <v>是</v>
       </c>
       <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>是</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>goal3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -727,318 +1157,498 @@
         <v>目标系统</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>日常活动和评价与班级目标保持一致。</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G4" t="str">
-        <v>是</v>
-      </c>
-      <c r="H4" t="str">
-        <v>1</v>
-      </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>是</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>org1</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>班干部岗位职责清楚且能稳定运转。</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G5" t="str">
-        <v>是</v>
-      </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
       <c r="I5" t="str">
         <v>是</v>
       </c>
       <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>是</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>org2</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>班级事务能够由学生参与分工，而非全部由教师承担。</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G6" t="str">
-        <v>是</v>
-      </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
       <c r="I6" t="str">
         <v>是</v>
       </c>
       <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>是</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>org3</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>班级日常关键节点有明确的执行流程。</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G7" t="str">
-        <v>是</v>
-      </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
       <c r="I7" t="str">
         <v>是</v>
       </c>
       <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>是</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>act1</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>班级活动能够回应学生真实需要。</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G8" t="str">
-        <v>是</v>
-      </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
       <c r="I8" t="str">
         <v>是</v>
       </c>
       <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>是</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>act2</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>活动结束后会进行简短复盘并形成改进。</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G9" t="str">
-        <v>是</v>
-      </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>是</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>act3</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>多数学生都有参与和承担责任的机会。</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G10" t="str">
-        <v>是</v>
-      </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
       <c r="I10" t="str">
         <v>是</v>
       </c>
       <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>是</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B11" t="str">
-        <v>env1</v>
+        <v>q10</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>班级空间和信息布置能够支持秩序与学习。</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G11" t="str">
-        <v>是</v>
-      </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
       <c r="I11" t="str">
         <v>是</v>
       </c>
       <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>是</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B12" t="str">
-        <v>env2</v>
+        <v>q11</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
       </c>
       <c r="D12" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>班级规则由师生共同理解而非只贴在墙上。</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G12" t="str">
-        <v>是</v>
-      </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
       <c r="I12" t="str">
         <v>是</v>
       </c>
       <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>是</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B13" t="str">
-        <v>env3</v>
+        <v>q12</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
       </c>
       <c r="D13" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>出现混乱时能够快速恢复稳定节奏。</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G13" t="str">
-        <v>是</v>
-      </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
       <c r="I13" t="str">
         <v>是</v>
       </c>
       <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>是</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B14" t="str">
-        <v>rel1</v>
+        <v>q13</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1047,30 +1657,48 @@
         <v>关系系统</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>学生普遍感到被尊重、被听见。</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G14" t="str">
-        <v>是</v>
-      </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
       <c r="I14" t="str">
         <v>是</v>
       </c>
       <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>是</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B15" t="str">
-        <v>rel2</v>
+        <v>q14</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1079,30 +1707,48 @@
         <v>关系系统</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>学生冲突能够被及时处理并修复关系。</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G15" t="str">
-        <v>是</v>
-      </c>
-      <c r="H15" t="str">
-        <v>1</v>
-      </c>
       <c r="I15" t="str">
         <v>是</v>
       </c>
       <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>是</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B16" t="str">
-        <v>rel3</v>
+        <v>q15</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1111,30 +1757,48 @@
         <v>关系系统</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>班级中存在稳定的互助和同伴支持。</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G16" t="str">
-        <v>是</v>
-      </c>
-      <c r="H16" t="str">
-        <v>1</v>
-      </c>
       <c r="I16" t="str">
         <v>是</v>
       </c>
       <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>是</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B17" t="str">
-        <v>en1</v>
+        <v>q1</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1143,30 +1807,48 @@
         <v>秩序能量</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>我不在教室时，班级秩序仍能维持。</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G17" t="str">
-        <v>是</v>
-      </c>
-      <c r="H17" t="str">
-        <v>1</v>
-      </c>
       <c r="I17" t="str">
         <v>是</v>
       </c>
       <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>是</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B18" t="str">
-        <v>en2</v>
+        <v>q2</v>
       </c>
       <c r="C18" t="str">
         <v>single</v>
@@ -1175,30 +1857,48 @@
         <v>秩序能量</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>课间到上课的过渡不需要我反复提醒。</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G18" t="str">
-        <v>是</v>
-      </c>
-      <c r="H18" t="str">
-        <v>1</v>
-      </c>
       <c r="I18" t="str">
         <v>是</v>
       </c>
       <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>是</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B19" t="str">
-        <v>en3</v>
+        <v>q3</v>
       </c>
       <c r="C19" t="str">
         <v>single</v>
@@ -1207,30 +1907,48 @@
         <v>学习能量</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>多数学生在自习时能自主投入。</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G19" t="str">
-        <v>是</v>
-      </c>
-      <c r="H19" t="str">
-        <v>1</v>
-      </c>
       <c r="I19" t="str">
         <v>是</v>
       </c>
       <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>是</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B20" t="str">
-        <v>en4</v>
+        <v>q4</v>
       </c>
       <c r="C20" t="str">
         <v>single</v>
@@ -1239,30 +1957,48 @@
         <v>学习能量</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>学生会主动追问自己不懂的问题。</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G20" t="str">
-        <v>是</v>
-      </c>
-      <c r="H20" t="str">
-        <v>1</v>
-      </c>
       <c r="I20" t="str">
         <v>是</v>
       </c>
       <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>是</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B21" t="str">
-        <v>en5</v>
+        <v>q5</v>
       </c>
       <c r="C21" t="str">
         <v>single</v>
@@ -1271,30 +2007,48 @@
         <v>联结能量</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>学生之间会自发互相帮助。</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G21" t="str">
-        <v>是</v>
-      </c>
-      <c r="H21" t="str">
-        <v>1</v>
-      </c>
       <c r="I21" t="str">
         <v>是</v>
       </c>
       <c r="J21" t="str">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>是</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>compute</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B22" t="str">
-        <v>en6</v>
+        <v>q6</v>
       </c>
       <c r="C22" t="str">
         <v>single</v>
@@ -1303,27 +2057,545 @@
         <v>联结能量</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>新转入的学生能较快融入集体。</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G22" t="str">
-        <v>是</v>
-      </c>
-      <c r="H22" t="str">
-        <v>1</v>
-      </c>
       <c r="I22" t="str">
         <v>是</v>
       </c>
       <c r="J22" t="str">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>是</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>compute</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B23" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>single</v>
+      </c>
+      <c r="D23" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>最近两周，班级里学生或家长的情绪被反复压制、没有表达出口的频率？</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I23" t="str">
+        <v>否</v>
+      </c>
+      <c r="J23" t="str">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>是</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C24" t="str">
+        <v>single</v>
+      </c>
+      <c r="D24" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>最近两周，班级冲突被掩盖或回避、没有正式解决路径的频率？</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I24" t="str">
+        <v>否</v>
+      </c>
+      <c r="J24" t="str">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>是</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B25" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C25" t="str">
+        <v>single</v>
+      </c>
+      <c r="D25" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>最近两周，学生或家长的真实需求提出后长期得不到回应的频率？</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I25" t="str">
+        <v>否</v>
+      </c>
+      <c r="J25" t="str">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>是</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B26" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C26" t="str">
+        <v>single</v>
+      </c>
+      <c r="D26" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>最近两周，班级里部分学生的声音完全听不到、被边缘化的频率？</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I26" t="str">
+        <v>否</v>
+      </c>
+      <c r="J26" t="str">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>是</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B27" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>single</v>
+      </c>
+      <c r="D27" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>活动目标在开始前已经明确传达给所有参与者。</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I27" t="str">
+        <v>否</v>
+      </c>
+      <c r="J27" t="str">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>是</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B28" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>single</v>
+      </c>
+      <c r="D28" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>各岗位分工在活动前已经落实到具体的人。</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I28" t="str">
+        <v>否</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>是</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B29" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C29" t="str">
+        <v>single</v>
+      </c>
+      <c r="D29" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>活动现场的秩序基本由既定规则维持。</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I29" t="str">
+        <v>否</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>是</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B30" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C30" t="str">
+        <v>single</v>
+      </c>
+      <c r="D30" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>参与者对活动流程的熟悉程度足够。</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I30" t="str">
+        <v>否</v>
+      </c>
+      <c r="J30" t="str">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>是</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B31" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C31" t="str">
+        <v>single</v>
+      </c>
+      <c r="D31" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>活动中的突发情况能在现场快速处理。</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I31" t="str">
+        <v>否</v>
+      </c>
+      <c r="J31" t="str">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>是</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B32" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C32" t="str">
+        <v>single</v>
+      </c>
+      <c r="D32" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>活动结束后有复盘和资料归档。</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I32" t="str">
+        <v>否</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>是</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1348,13 +2620,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1362,13 +2634,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1376,13 +2648,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1390,13 +2662,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1404,13 +2676,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
@@ -1418,13 +2690,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B7" t="str">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>完全不符合</v>
+        <v>几乎没有</v>
       </c>
       <c r="D7" t="str">
         <v>1</v>
@@ -1432,13 +2704,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B8" t="str">
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>比较不符合</v>
+        <v>很少</v>
       </c>
       <c r="D8" t="str">
         <v>2</v>
@@ -1446,13 +2718,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B9" t="str">
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>一般</v>
+        <v>有时</v>
       </c>
       <c r="D9" t="str">
         <v>3</v>
@@ -1460,13 +2732,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B10" t="str">
         <v>4</v>
       </c>
       <c r="C10" t="str">
-        <v>比较符合</v>
+        <v>经常</v>
       </c>
       <c r="D10" t="str">
         <v>4</v>
@@ -1474,13 +2746,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B11" t="str">
         <v>5</v>
       </c>
       <c r="C11" t="str">
-        <v>非常符合</v>
+        <v>几乎每天</v>
       </c>
       <c r="D11" t="str">
         <v>5</v>
@@ -1495,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1525,19 +2797,25 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>CS_GOAL</v>
+        <v>CS_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>目标系统</v>
       </c>
       <c r="D2" t="str">
-        <v>goal1,goal2,goal3</v>
+        <v>q1,q2,q3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1554,19 +2832,25 @@
       <c r="I2" t="str">
         <v>目标清晰且已落地</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>CS_ORG</v>
+        <v>CS_S1D2</v>
       </c>
       <c r="C3" t="str">
-        <v>组织系统</v>
+        <v>权力系统</v>
       </c>
       <c r="D3" t="str">
-        <v>org1,org2,org3</v>
+        <v>q4,q5,q6</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1575,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>组织系统维度</v>
+        <v>权力系统维度</v>
       </c>
       <c r="H3" t="str">
         <v>岗位职责不清，事务集中在教师身上</v>
@@ -1583,19 +2867,25 @@
       <c r="I3" t="str">
         <v>学生分工稳定运转</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>CS_ACTIVITY</v>
+        <v>CS_S1D3</v>
       </c>
       <c r="C4" t="str">
-        <v>活动系统</v>
+        <v>情感系统</v>
       </c>
       <c r="D4" t="str">
-        <v>act1,act2,act3</v>
+        <v>q7,q8,q9</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1604,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>活动系统维度</v>
+        <v>情感系统维度</v>
       </c>
       <c r="H4" t="str">
         <v>活动脱离学生真实需要且缺少复盘</v>
@@ -1612,19 +2902,25 @@
       <c r="I4" t="str">
         <v>活动有回应、有复盘</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>CS_ENV</v>
+        <v>CS_S1D4</v>
       </c>
       <c r="C5" t="str">
-        <v>环境系统</v>
+        <v>规范系统</v>
       </c>
       <c r="D5" t="str">
-        <v>env1,env2,env3</v>
+        <v>q10,q11,q12</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1633,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>环境系统维度</v>
+        <v>规范系统维度</v>
       </c>
       <c r="H5" t="str">
         <v>规则停留在墙上，混乱后难以恢复</v>
@@ -1641,19 +2937,25 @@
       <c r="I5" t="str">
         <v>环境与规则支持秩序</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>CS_RELATION</v>
+        <v>CS_S1D5</v>
       </c>
       <c r="C6" t="str">
         <v>关系系统</v>
       </c>
       <c r="D6" t="str">
-        <v>rel1,rel2,rel3</v>
+        <v>q13,q14,q15</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1670,19 +2972,25 @@
       <c r="I6" t="str">
         <v>关系稳定，学生被听见</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>CS_ORDER</v>
+        <v>CS_S2D1</v>
       </c>
       <c r="C7" t="str">
         <v>秩序能量</v>
       </c>
       <c r="D7" t="str">
-        <v>en1,en2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1699,19 +3007,25 @@
       <c r="I7" t="str">
         <v>秩序可自主维持</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>CS_LEARNING</v>
+        <v>CS_S2D2</v>
       </c>
       <c r="C8" t="str">
         <v>学习能量</v>
       </c>
       <c r="D8" t="str">
-        <v>en3,en4</v>
+        <v>q3,q4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -1728,19 +3042,25 @@
       <c r="I8" t="str">
         <v>学习氛围自发</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>CS_CONNECT</v>
+        <v>CS_S2D3</v>
       </c>
       <c r="C9" t="str">
         <v>联结能量</v>
       </c>
       <c r="D9" t="str">
-        <v>en5,en6</v>
+        <v>q5,q6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -1757,10 +3077,121 @@
       <c r="I9" t="str">
         <v>同伴联结紧密</v>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B10" t="str">
+        <v>CS_S3D1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>截断信号</v>
+      </c>
+      <c r="D10" t="str">
+        <v>q1,q2,q3,q4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>四类截断信号的总体频率，越高越接近爆发临界</v>
+      </c>
+      <c r="H10" t="str">
+        <v>信号频繁被截断，堰塞湖蓄积风险高</v>
+      </c>
+      <c r="I10" t="str">
+        <v>信号有正常表达出口</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B11" t="str">
+        <v>CS_S4D1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>组织分工</v>
+      </c>
+      <c r="D11" t="str">
+        <v>q1,q2,q6</v>
+      </c>
+      <c r="E11" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>CS_S4D2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>秩序系统</v>
+      </c>
+      <c r="D12" t="str">
+        <v>q3,q4,q5</v>
+      </c>
+      <c r="E12" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/assessment.xlsx
+++ b/business-libraries/test-data/class_system/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -523,16 +523,16 @@
         <v>CS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>班级五系统速评</v>
+        <v>五系统自评表</v>
       </c>
       <c r="C2" t="str">
-        <v>五系统速评</v>
+        <v>五系统自评</v>
       </c>
       <c r="D2" t="str">
         <v>class_system</v>
       </c>
       <c r="E2" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -565,10 +565,10 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>每两周一次；学期初/中/末必做</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>14</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -598,16 +598,16 @@
         <v/>
       </c>
       <c r="AA2" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB2" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC2" t="str">
-        <v>每个系统三道题，定位当前最需要建设的班级子系统。反向计分：得分越高表示越薄弱。</v>
+        <v>A01 五系统自评表（班主任自评·15题）：关系/组织/规范/目标/情感五个系统各3题，1-5分加总15-75分。四档解读：60-75健康 / 45-59关注(挑1-2弱项4周专项) / 30-44系统性问题(启动重建+分层干预) / &lt;30立即介入(学校支援)。适用：每两周一次。</v>
       </c>
       <c r="AD2" t="str">
-        <v/>
+        <v>总分15-75：60-75健康 / 45-59关注 / 30-44系统性问题 / &lt;30立即介入</v>
       </c>
       <c r="AE2" t="str">
         <v/>
@@ -639,16 +639,16 @@
         <v>CS_S2</v>
       </c>
       <c r="B3" t="str">
-        <v>班级能量场问卷</v>
+        <v>班级能量场问卷·教师版</v>
       </c>
       <c r="C3" t="str">
-        <v>能量场</v>
+        <v>能量场·教师版</v>
       </c>
       <c r="D3" t="str">
         <v>class_system</v>
       </c>
       <c r="E3" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -666,13 +666,13 @@
         <v>manual</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>monthly</v>
       </c>
       <c r="L3" t="str">
         <v>否</v>
       </c>
       <c r="M3" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -681,10 +681,10 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>五系统自评整体偏弱或关系维度突出时施测</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="R3" t="str">
         <v>CS_S1</v>
@@ -693,10 +693,10 @@
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[CS_S1].均分 &gt;= 3.2 或 量表[CS_S1].维度[CS_S1D5] &gt;= 3.5</v>
+        <v>量表[CS_S1].均分 &lt;= 3.6 或 量表[CS_S1].维度[CS_S1D1] &lt;= 3.5</v>
       </c>
       <c r="U3" t="str">
-        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
+        <v>五系统自评均分≤3.6 或关系系统≤3.5 时，建议做能量场问卷（教师版）看具体维度表现</v>
       </c>
       <c r="V3" t="str">
         <v>teacher_only</v>
@@ -714,13 +714,13 @@
         <v/>
       </c>
       <c r="AA3" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB3" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>五大系统整体偏弱、或师生关系维度突出时，再往下测班级能量场</v>
+        <v>A02-T 班级能量场问卷（教师版·25题）：教师评价班级能量场，五维情感/认知/行为/关系/环境，1-5 Likert 非常符合=5；反向题（题2/7/21/23）按 6−原始分 转换。环境维度信度不足，降为筛查层，不计入五维综合均值。</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -755,16 +755,16 @@
         <v>CS_S3</v>
       </c>
       <c r="B4" t="str">
-        <v>堰塞湖四信号自查</v>
+        <v>班级能量场问卷·学生版</v>
       </c>
       <c r="C4" t="str">
-        <v>堰塞湖自查</v>
+        <v>能量场·学生版</v>
       </c>
       <c r="D4" t="str">
         <v>class_system</v>
       </c>
       <c r="E4" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>teacher</v>
+        <v>student</v>
       </c>
       <c r="I4" t="str">
         <v>self_report</v>
@@ -782,13 +782,13 @@
         <v>manual</v>
       </c>
       <c r="K4" t="str">
-        <v>per_case</v>
+        <v>monthly</v>
       </c>
       <c r="L4" t="str">
         <v>否</v>
       </c>
       <c r="M4" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -797,22 +797,22 @@
         <v/>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>教师版施测后需学生视角交叉验证时</v>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="R4" t="str">
-        <v>CS_S1</v>
+        <v>CS_S2</v>
       </c>
       <c r="S4" t="str">
         <v/>
       </c>
       <c r="T4" t="str">
-        <v>量表[CS_S1].均分 &gt;= 3.2</v>
+        <v>量表[CS_S2].均分 &lt;= 3.5 或 量表[CS_S2].维度[CS_S2D4] &lt;= 3.5</v>
       </c>
       <c r="U4" t="str">
-        <v>五系统速评均分 ≥ 3.2 时建议做一次堰塞湖自查，排查班级是否有被截断的信号</v>
+        <v>能量场问卷（教师版）均分≤3.5 或关系维度≤3.5 时，建议再做学生版交叉验证</v>
       </c>
       <c r="V4" t="str">
         <v>teacher_only</v>
@@ -830,13 +830,13 @@
         <v/>
       </c>
       <c r="AA4" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB4" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC4" t="str">
-        <v>班级层面预警自查：情绪、冲突、需求、声音四类信号被截断时，问题会在水面下蓄积，最终以突发方式爆发。信号频率越高越需要及时疏解。</v>
+        <v>A02-S 班级能量场问卷（学生版·25题）：学生自评自身体验，计分同教师版（反向题2/7/21/23按 6−v 转换）。学生版维度归组与教师版不同：情感1-5 / 关系6,7,11-15,24 / 认知8-10,17,22 / 行为16,18-21 / 环境23,25。⚠️ 学生自陈题干与逐题维度归组为本次整理推断的 draft，待学校定稿。学生问卷须匿名、班主任回避。</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -860,7 +860,7 @@
         <v/>
       </c>
       <c r="AK4" t="str">
-        <v>专项/情境</v>
+        <v>深度诊断</v>
       </c>
       <c r="AL4" t="str">
         <v>定位薄弱维度，匹配对应工具</v>
@@ -871,16 +871,16 @@
         <v>CS_S4</v>
       </c>
       <c r="B5" t="str">
-        <v>大型活动组织专项评估</v>
+        <v>进班观测速记卡</v>
       </c>
       <c r="C5" t="str">
-        <v>大型活动组织专项</v>
+        <v>进班观测</v>
       </c>
       <c r="D5" t="str">
         <v>class_system</v>
       </c>
       <c r="E5" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -892,19 +892,19 @@
         <v>teacher</v>
       </c>
       <c r="I5" t="str">
-        <v>self_report</v>
+        <v>observation</v>
       </c>
       <c r="J5" t="str">
         <v>manual</v>
       </c>
       <c r="K5" t="str">
-        <v>monthly</v>
+        <v>weekly</v>
       </c>
       <c r="L5" t="str">
         <v>否</v>
       </c>
       <c r="M5" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>每周2-3次进班时快速记录</v>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>7</v>
       </c>
       <c r="R5" t="str">
         <v>CS_S1</v>
@@ -925,10 +925,10 @@
         <v/>
       </c>
       <c r="T5" t="str">
-        <v>量表[CS_S1].维度[CS_S1D2] &gt;= 3.2</v>
+        <v>量表[CS_S1].均分 &lt;= 3.6</v>
       </c>
       <c r="U5" t="str">
-        <v>权力系统维度偏高时才需要做大型活动专项评估</v>
+        <v>五系统自评均分≤3.6 时，建议每周用进班观测速记卡追踪趋势</v>
       </c>
       <c r="V5" t="str">
         <v>teacher_only</v>
@@ -946,13 +946,13 @@
         <v/>
       </c>
       <c r="AA5" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB5" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC5" t="str">
-        <v>班级组织大型活动（运动会、汇演、外出实践等）前的专项评估。</v>
+        <v>A03 进班观测速记卡（每周2-3次）：按五维锚点做 1-3 快速勾选，周追踪趋势，配合能量场问卷使用。走进教室第一感觉即最真实数据，非检查而是感受。环境为筛查层，不计入能量场综合均值。</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -982,16 +982,712 @@
         <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>能量场五维评分锚点表</v>
+      </c>
+      <c r="C6" t="str">
+        <v>五维锚点</v>
+      </c>
+      <c r="D6" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E6" t="str">
+        <v>primary</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I6" t="str">
+        <v>observation</v>
+      </c>
+      <c r="J6" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K6" t="str">
+        <v>weekly</v>
+      </c>
+      <c r="L6" t="str">
+        <v>否</v>
+      </c>
+      <c r="M6" t="str">
+        <v>3</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v>配合进班观测速记卡做半定量评级</v>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v>量表[CS_S4].均分 &lt;= 2.5</v>
+      </c>
+      <c r="U6" t="str">
+        <v>进班观测速记卡均分≤2.5 时，用五维锚点表做半定量评级</v>
+      </c>
+      <c r="V6" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W6" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X6" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>A04 能量场五维评分锚点表：五维 1/3/5 锚点描述（半定量），快速评级 1=低能量 5=高能量，配合进班观测速记卡使用。环境为筛查层。</v>
+      </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <v/>
+      </c>
+      <c r="AF6" t="str">
+        <v/>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
+      <c r="AJ6" t="str">
+        <v/>
+      </c>
+      <c r="AK6" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>心理风险A-E点检表</v>
+      </c>
+      <c r="C7" t="str">
+        <v>A-E点检</v>
+      </c>
+      <c r="D7" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E7" t="str">
+        <v>primary</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I7" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="J7" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K7" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L7" t="str">
+        <v>否</v>
+      </c>
+      <c r="M7" t="str">
+        <v>3</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>出现风险信号或班级系统性问题时点检</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>14</v>
+      </c>
+      <c r="R7" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v>量表[CS_S1].均分 &lt;= 3 或 量表[CS_S1].维度[CS_S1D1] &lt;= 3</v>
+      </c>
+      <c r="U7" t="str">
+        <v>五系统自评均分≤3 或关系系统≤3 时，建议做心理风险 A-E 点检排查个体风险</v>
+      </c>
+      <c r="V7" t="str">
+        <v>psychologist</v>
+      </c>
+      <c r="W7" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X7" t="str">
+        <v>highly_sensitive</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>A05 心理风险 A-E 级点检表（班主任/心理教师）：等级判定（典型表现+量化指标），响应动作分级。重要原则：A/B 级必须第一时间上报学校，不能由班主任独自处理；E 级为健康观察·月度追踪。</v>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v/>
+      </c>
+      <c r="AF7" t="str">
+        <v/>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
+      <c r="AJ7" t="str">
+        <v/>
+      </c>
+      <c r="AK7" t="str">
+        <v>红线检查</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>绘画投射筛查</v>
+      </c>
+      <c r="C8" t="str">
+        <v>绘画筛查</v>
+      </c>
+      <c r="D8" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E8" t="str">
+        <v>primary</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I8" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="J8" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K8" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L8" t="str">
+        <v>否</v>
+      </c>
+      <c r="M8" t="str">
+        <v>10</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>心理教师对疑似风险学生做绘画投射筛查时</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v>量表[CS_S6].题[q3] == 1 或 量表[CS_S6].题[q2] == 1</v>
+      </c>
+      <c r="U8" t="str">
+        <v>A-E 点检命中 C 级或 B 级时，建议心理教师用绘画投射筛查进一步评估风险</v>
+      </c>
+      <c r="V8" t="str">
+        <v>psychologist</v>
+      </c>
+      <c r="W8" t="str">
+        <v>心理教师</v>
+      </c>
+      <c r="X8" t="str">
+        <v>highly_sensitive</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>A06 绘画投射筛查指标（HTP/雨中人/树木画，心理教师使用）：红旗清单判定风险等级 红/橙/黄/绿，红=高危需转介、橙=中风险关注、黄=轻度提示、绿=保护性因素（降级）。使用边界：筛查与转介建议，非诊断结论。</v>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
+        <v/>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8" t="str">
+        <v/>
+      </c>
+      <c r="AJ8" t="str">
+        <v/>
+      </c>
+      <c r="AK8" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>依恋关系观察清单</v>
+      </c>
+      <c r="C9" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="D9" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E9" t="str">
+        <v>primary</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I9" t="str">
+        <v>observation</v>
+      </c>
+      <c r="J9" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K9" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L9" t="str">
+        <v>否</v>
+      </c>
+      <c r="M9" t="str">
+        <v>10</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>每学期开学前3周完成全班依恋观察评估</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v>量表[CS_S1].维度[CS_S1D1] &lt;= 3.5</v>
+      </c>
+      <c r="U9" t="str">
+        <v>五系统自评关系系统≤3.5 时，建议做全班依恋关系观察评估</v>
+      </c>
+      <c r="V9" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W9" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X9" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>A07 依恋关系观察清单（班主任）：每学期开学前 3 周完成全班依恋观察评估。家庭背景五问（访谈）+ 四类识别（安全/A回避/C焦虑-矛盾/D混乱）+ 快速观察清单 7 维度。D 型须警惕创伤背景，及时转介。理论 Bowlby 1969 / Ainsworth 1978。</v>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
+        <v/>
+      </c>
+      <c r="AG9" t="str">
+        <v/>
+      </c>
+      <c r="AH9" t="str">
+        <v/>
+      </c>
+      <c r="AI9" t="str">
+        <v/>
+      </c>
+      <c r="AJ9" t="str">
+        <v/>
+      </c>
+      <c r="AK9" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>个案诊断矩阵</v>
+      </c>
+      <c r="C10" t="str">
+        <v>个案诊断</v>
+      </c>
+      <c r="D10" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E10" t="str">
+        <v>primary</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I10" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="J10" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K10" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L10" t="str">
+        <v>否</v>
+      </c>
+      <c r="M10" t="str">
+        <v>5</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>出现个体学生行为问题时</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v>量表[CS_S1].均分 &lt;= 3.6 或 量表[CS_S1].维度[CS_S1D4] &lt;= 3.5</v>
+      </c>
+      <c r="U10" t="str">
+        <v>五系统自评均分≤3.6 或目标系统≤3.5 时，对个体行为问题做能力×意愿个案诊断</v>
+      </c>
+      <c r="V10" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W10" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X10" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>A08 个案诊断矩阵（能力×意愿）：双轴诊断 能力(会不会)×意愿(想不想) → 四类型匹配干预（成功/挫折/对抗/放弃型）。适用：出现个体行为问题时。另含第二诊断维度「情境vs模式」与「诊断四步法」（见手册）。</v>
+      </c>
+      <c r="AD10" t="str">
+        <v/>
+      </c>
+      <c r="AE10" t="str">
+        <v/>
+      </c>
+      <c r="AF10" t="str">
+        <v/>
+      </c>
+      <c r="AG10" t="str">
+        <v/>
+      </c>
+      <c r="AH10" t="str">
+        <v/>
+      </c>
+      <c r="AI10" t="str">
+        <v/>
+      </c>
+      <c r="AJ10" t="str">
+        <v/>
+      </c>
+      <c r="AK10" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SDQ小学生心理筛查量表（使用指引）</v>
+      </c>
+      <c r="C11" t="str">
+        <v>SDQ指引</v>
+      </c>
+      <c r="D11" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E11" t="str">
+        <v>primary</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I11" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="J11" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K11" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L11" t="str">
+        <v>否</v>
+      </c>
+      <c r="M11" t="str">
+        <v>10</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v>发现隐形焦虑/情绪症状学生，需筛查确认时</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v>量表[CS_S6].题[q4] == 1 或 量表[CS_S6].题[q5] == 1</v>
+      </c>
+      <c r="U11" t="str">
+        <v>A-E 点检命中 D 级或 E 级（疑似隐形情绪症状）时，建议用 SDQ 筛查确认</v>
+      </c>
+      <c r="V11" t="str">
+        <v>psychologist</v>
+      </c>
+      <c r="W11" t="str">
+        <v>心理教师</v>
+      </c>
+      <c r="X11" t="str">
+        <v>highly_sensitive</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>external</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>外部量表（Goodman SDQ），题项与常模须引用原版权方；严禁公开宣读或贴标签</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>A09 SDQ 小学生心理筛查量表（使用指引·外部量表）：R. Goodman 编制的优势与困难问卷，5 维度 25 题。⚠️ 仅给使用指引，题项与常模须引用原版权方，不标为我方原创。用于发现隐形焦虑/情绪症状学生，异常者启动 B/C 级响应；群体筛查维度均分&gt;4 提示班级系统性问题。</v>
+      </c>
+      <c r="AD11" t="str">
+        <v/>
+      </c>
+      <c r="AE11" t="str">
+        <v/>
+      </c>
+      <c r="AF11" t="str">
+        <v/>
+      </c>
+      <c r="AG11" t="str">
+        <v/>
+      </c>
+      <c r="AH11" t="str">
+        <v/>
+      </c>
+      <c r="AI11" t="str">
+        <v/>
+      </c>
+      <c r="AJ11" t="str">
+        <v/>
+      </c>
+      <c r="AK11" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1054,13 +1750,13 @@
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>目标系统</v>
+        <v>关系系统</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>学生清楚本班共同目标以及为什么要实现它。</v>
+        <v>学生之间愿意互相帮助</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -1069,7 +1765,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J2" t="str">
         <v>1</v>
@@ -1104,13 +1800,13 @@
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>目标系统</v>
+        <v>关系系统</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>班级目标已转化为本学期可观察的里程碑。</v>
+        <v>班级有温暖、友爱的氛围</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -1119,7 +1815,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I3" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J3" t="str">
         <v>1</v>
@@ -1154,13 +1850,13 @@
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>目标系统</v>
+        <v>关系系统</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>日常活动和评价与班级目标保持一致。</v>
+        <v>弱势学生不被孤立或欺负</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -1169,7 +1865,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J4" t="str">
         <v>1</v>
@@ -1204,13 +1900,13 @@
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>权力系统</v>
+        <v>组织系统</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>班干部岗位职责清楚且能稳定运转。</v>
+        <v>班委有真正的服务意识</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -1219,7 +1915,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J5" t="str">
         <v>1</v>
@@ -1254,13 +1950,13 @@
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>权力系统</v>
+        <v>组织系统</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>班级事务能够由学生参与分工，而非全部由教师承担。</v>
+        <v>普通学生有参与班级事务的渠道</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -1269,7 +1965,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I6" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J6" t="str">
         <v>1</v>
@@ -1304,13 +2000,13 @@
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>权力系统</v>
+        <v>组织系统</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>班级日常关键节点有明确的执行流程。</v>
+        <v>没有学生被“边缘化”</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -1319,7 +2015,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J7" t="str">
         <v>1</v>
@@ -1354,13 +2050,13 @@
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>情感系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>班级活动能够回应学生真实需要。</v>
+        <v>学生认同班级规则</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1369,7 +2065,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J8" t="str">
         <v>1</v>
@@ -1404,13 +2100,13 @@
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>情感系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>活动结束后会进行简短复盘并形成改进。</v>
+        <v>规则执行一致、公平</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -1419,7 +2115,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I9" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J9" t="str">
         <v>1</v>
@@ -1454,13 +2150,13 @@
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>情感系统</v>
+        <v>规范系统</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>多数学生都有参与和承担责任的机会。</v>
+        <v>规则有弹性、能适应特殊情况</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1469,7 +2165,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J10" t="str">
         <v>1</v>
@@ -1504,13 +2200,13 @@
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>规范系统</v>
+        <v>目标系统</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>班级空间和信息布置能够支持秩序与学习。</v>
+        <v>学生有学习目标和动力</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1519,7 +2215,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J11" t="str">
         <v>1</v>
@@ -1554,13 +2250,13 @@
         <v>single</v>
       </c>
       <c r="D12" t="str">
-        <v>规范系统</v>
+        <v>目标系统</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>班级规则由师生共同理解而非只贴在墙上。</v>
+        <v>班级有共同的进步目标</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1569,7 +2265,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I12" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J12" t="str">
         <v>1</v>
@@ -1604,13 +2300,13 @@
         <v>single</v>
       </c>
       <c r="D13" t="str">
-        <v>规范系统</v>
+        <v>目标系统</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>出现混乱时能够快速恢复稳定节奏。</v>
+        <v>班级目标能凝聚大家的力量</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1619,7 +2315,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I13" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J13" t="str">
         <v>1</v>
@@ -1654,13 +2350,13 @@
         <v>single</v>
       </c>
       <c r="D14" t="str">
-        <v>关系系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>学生普遍感到被尊重、被听见。</v>
+        <v>学生愿意来学校</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1669,7 +2365,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J14" t="str">
         <v>1</v>
@@ -1704,13 +2400,13 @@
         <v>single</v>
       </c>
       <c r="D15" t="str">
-        <v>关系系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>学生冲突能够被及时处理并修复关系。</v>
+        <v>学生遇到问题会求助</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1719,7 +2415,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I15" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J15" t="str">
         <v>1</v>
@@ -1754,13 +2450,13 @@
         <v>single</v>
       </c>
       <c r="D16" t="str">
-        <v>关系系统</v>
+        <v>情感系统</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>班级中存在稳定的互助和同伴支持。</v>
+        <v>班级有集体荣誉感</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1769,7 +2465,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J16" t="str">
         <v>1</v>
@@ -1804,13 +2500,13 @@
         <v>single</v>
       </c>
       <c r="D17" t="str">
-        <v>秩序能量</v>
+        <v>情感</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>我不在教室时，班级秩序仍能维持。</v>
+        <v>积极课堂氛围</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1819,7 +2515,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I17" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J17" t="str">
         <v>1</v>
@@ -1854,13 +2550,13 @@
         <v>single</v>
       </c>
       <c r="D18" t="str">
-        <v>秩序能量</v>
+        <v>情感</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>课间到上课的过渡不需要我反复提醒。</v>
+        <v>学生表情放松</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1884,7 +2580,7 @@
         <v>compute</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>反向题：按 6−原始分 转换后计入维度</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1904,13 +2600,13 @@
         <v>single</v>
       </c>
       <c r="D19" t="str">
-        <v>学习能量</v>
+        <v>情感</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>多数学生在自习时能自主投入。</v>
+        <v>教师心理压力小</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1919,7 +2615,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I19" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J19" t="str">
         <v>1</v>
@@ -1954,13 +2650,13 @@
         <v>single</v>
       </c>
       <c r="D20" t="str">
-        <v>学习能量</v>
+        <v>情感</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>学生会主动追问自己不懂的问题。</v>
+        <v>被学生接纳愉悦感</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1969,7 +2665,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I20" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J20" t="str">
         <v>1</v>
@@ -2004,13 +2700,13 @@
         <v>single</v>
       </c>
       <c r="D21" t="str">
-        <v>联结能量</v>
+        <v>情感</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>学生之间会自发互相帮助。</v>
+        <v>有效帮助学生成就感</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -2019,7 +2715,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I21" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J21" t="str">
         <v>1</v>
@@ -2054,13 +2750,13 @@
         <v>single</v>
       </c>
       <c r="D22" t="str">
-        <v>联结能量</v>
+        <v>认知</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>新转入的学生能较快融入集体。</v>
+        <v>集体荣誉感</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -2069,7 +2765,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I22" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J22" t="str">
         <v>1</v>
@@ -2095,31 +2791,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CS_S3</v>
+        <v>CS_S2</v>
       </c>
       <c r="B23" t="str">
-        <v>q1</v>
+        <v>q7</v>
       </c>
       <c r="C23" t="str">
         <v>single</v>
       </c>
       <c r="D23" t="str">
-        <v>截断信号</v>
+        <v>认知</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>最近两周，班级里学生或家长的情绪被反复压制、没有表达出口的频率？</v>
+        <v>主动提规则建议</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I23" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J23" t="str">
         <v>1</v>
@@ -2134,7 +2830,7 @@
         <v>compute</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>反向题：按 6−原始分 转换后计入维度</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -2145,28 +2841,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CS_S3</v>
+        <v>CS_S2</v>
       </c>
       <c r="B24" t="str">
-        <v>q2</v>
+        <v>q8</v>
       </c>
       <c r="C24" t="str">
         <v>single</v>
       </c>
       <c r="D24" t="str">
-        <v>截断信号</v>
+        <v>认知</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>最近两周，班级冲突被掩盖或回避、没有正式解决路径的频率？</v>
+        <v>积极思考并回答</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I24" t="str">
         <v>否</v>
@@ -2195,28 +2891,28 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CS_S3</v>
+        <v>CS_S2</v>
       </c>
       <c r="B25" t="str">
-        <v>q3</v>
+        <v>q9</v>
       </c>
       <c r="C25" t="str">
         <v>single</v>
       </c>
       <c r="D25" t="str">
-        <v>截断信号</v>
+        <v>认知</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>最近两周，学生或家长的真实需求提出后长期得不到回应的频率？</v>
+        <v>有效订正错误</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I25" t="str">
         <v>否</v>
@@ -2245,28 +2941,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CS_S3</v>
+        <v>CS_S2</v>
       </c>
       <c r="B26" t="str">
-        <v>q4</v>
+        <v>q10</v>
       </c>
       <c r="C26" t="str">
         <v>single</v>
       </c>
       <c r="D26" t="str">
-        <v>截断信号</v>
+        <v>认知</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>最近两周，班级里部分学生的声音完全听不到、被边缘化的频率？</v>
+        <v>相信能提升班级</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I26" t="str">
         <v>否</v>
@@ -2295,22 +2991,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CS_S4</v>
+        <v>CS_S2</v>
       </c>
       <c r="B27" t="str">
-        <v>q1</v>
+        <v>q11</v>
       </c>
       <c r="C27" t="str">
         <v>single</v>
       </c>
       <c r="D27" t="str">
-        <v>组织分工</v>
+        <v>行为</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>活动目标在开始前已经明确传达给所有参与者。</v>
+        <v>主动举手提问</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2345,22 +3041,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>CS_S4</v>
+        <v>CS_S2</v>
       </c>
       <c r="B28" t="str">
-        <v>q2</v>
+        <v>q12</v>
       </c>
       <c r="C28" t="str">
         <v>single</v>
       </c>
       <c r="D28" t="str">
-        <v>组织分工</v>
+        <v>行为</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>各岗位分工在活动前已经落实到具体的人。</v>
+        <v>用表情回应教师</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2395,22 +3091,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>CS_S4</v>
+        <v>CS_S2</v>
       </c>
       <c r="B29" t="str">
-        <v>q3</v>
+        <v>q13</v>
       </c>
       <c r="C29" t="str">
         <v>single</v>
       </c>
       <c r="D29" t="str">
-        <v>秩序系统</v>
+        <v>行为</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>活动现场的秩序基本由既定规则维持。</v>
+        <v>集体任务参与积极</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2445,22 +3141,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>CS_S4</v>
+        <v>CS_S2</v>
       </c>
       <c r="B30" t="str">
-        <v>q4</v>
+        <v>q14</v>
       </c>
       <c r="C30" t="str">
         <v>single</v>
       </c>
       <c r="D30" t="str">
-        <v>秩序系统</v>
+        <v>行为</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>参与者对活动流程的熟悉程度足够。</v>
+        <v>指令响应迅速</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2495,22 +3191,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>CS_S4</v>
+        <v>CS_S2</v>
       </c>
       <c r="B31" t="str">
-        <v>q5</v>
+        <v>q15</v>
       </c>
       <c r="C31" t="str">
         <v>single</v>
       </c>
       <c r="D31" t="str">
-        <v>秩序系统</v>
+        <v>行为</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>活动中的突发情况能在现场快速处理。</v>
+        <v>提醒次数≤3次/节</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2545,22 +3241,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>CS_S4</v>
+        <v>CS_S2</v>
       </c>
       <c r="B32" t="str">
-        <v>q6</v>
+        <v>q16</v>
       </c>
       <c r="C32" t="str">
         <v>single</v>
       </c>
       <c r="D32" t="str">
-        <v>组织分工</v>
+        <v>行为</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>活动结束后有复盘和资料归档。</v>
+        <v>主动维护秩序</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2593,16 +3289,4466 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C33" t="str">
+        <v>single</v>
+      </c>
+      <c r="D33" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>行为规范有礼貌</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I33" t="str">
+        <v>否</v>
+      </c>
+      <c r="J33" t="str">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>是</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B34" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C34" t="str">
+        <v>single</v>
+      </c>
+      <c r="D34" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>同学相处融洽</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I34" t="str">
+        <v>否</v>
+      </c>
+      <c r="J34" t="str">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>是</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B35" t="str">
+        <v>q19</v>
+      </c>
+      <c r="C35" t="str">
+        <v>single</v>
+      </c>
+      <c r="D35" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>包容回答偏差</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I35" t="str">
+        <v>否</v>
+      </c>
+      <c r="J35" t="str">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>是</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B36" t="str">
+        <v>q20</v>
+      </c>
+      <c r="C36" t="str">
+        <v>single</v>
+      </c>
+      <c r="D36" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>学习互助</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I36" t="str">
+        <v>否</v>
+      </c>
+      <c r="J36" t="str">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>是</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B37" t="str">
+        <v>q21</v>
+      </c>
+      <c r="C37" t="str">
+        <v>single</v>
+      </c>
+      <c r="D37" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>倾听回应批评</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I37" t="str">
+        <v>是</v>
+      </c>
+      <c r="J37" t="str">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>是</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N37" t="str">
+        <v>反向题：按 6−原始分 转换后计入维度</v>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B38" t="str">
+        <v>q22</v>
+      </c>
+      <c r="C38" t="str">
+        <v>single</v>
+      </c>
+      <c r="D38" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>愿意与教师交流</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I38" t="str">
+        <v>否</v>
+      </c>
+      <c r="J38" t="str">
+        <v>1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>是</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B39" t="str">
+        <v>q23</v>
+      </c>
+      <c r="C39" t="str">
+        <v>single</v>
+      </c>
+      <c r="D39" t="str">
+        <v>环境</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>学习态度认真</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I39" t="str">
+        <v>是</v>
+      </c>
+      <c r="J39" t="str">
+        <v>1</v>
+      </c>
+      <c r="K39" t="str">
+        <v>是</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N39" t="str">
+        <v>反向题：按 6−原始分 转换后计入维度（环境为筛查层）</v>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B40" t="str">
+        <v>q24</v>
+      </c>
+      <c r="C40" t="str">
+        <v>single</v>
+      </c>
+      <c r="D40" t="str">
+        <v>环境</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>精神状态饱满</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I40" t="str">
+        <v>否</v>
+      </c>
+      <c r="J40" t="str">
+        <v>1</v>
+      </c>
+      <c r="K40" t="str">
+        <v>是</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="B41" t="str">
+        <v>q25</v>
+      </c>
+      <c r="C41" t="str">
+        <v>single</v>
+      </c>
+      <c r="D41" t="str">
+        <v>环境</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>求助而非放弃</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I41" t="str">
+        <v>否</v>
+      </c>
+      <c r="J41" t="str">
+        <v>1</v>
+      </c>
+      <c r="K41" t="str">
+        <v>是</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B42" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C42" t="str">
+        <v>single</v>
+      </c>
+      <c r="D42" t="str">
+        <v>情感</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>我们班的课堂氛围让我感到积极、愉快。</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I42" t="str">
+        <v>否</v>
+      </c>
+      <c r="J42" t="str">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>是</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B43" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C43" t="str">
+        <v>single</v>
+      </c>
+      <c r="D43" t="str">
+        <v>情感</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>在课堂或班级里，我经常感到紧张、不放松。</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I43" t="str">
+        <v>是</v>
+      </c>
+      <c r="J43" t="str">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>是</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N43" t="str">
+        <v>反向题：按 6−原始分 转换后计入维度</v>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B44" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C44" t="str">
+        <v>single</v>
+      </c>
+      <c r="D44" t="str">
+        <v>情感</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>在班级里我觉得轻松，没有太大的压力。</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I44" t="str">
+        <v>否</v>
+      </c>
+      <c r="J44" t="str">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>是</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C45" t="str">
+        <v>single</v>
+      </c>
+      <c r="D45" t="str">
+        <v>情感</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>我觉得自己被这个班集体接纳，是被欢迎的。</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I45" t="str">
+        <v>否</v>
+      </c>
+      <c r="J45" t="str">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
+        <v>是</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B46" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C46" t="str">
+        <v>single</v>
+      </c>
+      <c r="D46" t="str">
+        <v>情感</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>我在班里做的事能得到认可，让我有成就感。</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I46" t="str">
+        <v>否</v>
+      </c>
+      <c r="J46" t="str">
+        <v>1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>是</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B47" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C47" t="str">
+        <v>single</v>
+      </c>
+      <c r="D47" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>我为在这个班而自豪，有集体荣誉感。</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I47" t="str">
+        <v>否</v>
+      </c>
+      <c r="J47" t="str">
+        <v>1</v>
+      </c>
+      <c r="K47" t="str">
+        <v>是</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B48" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C48" t="str">
+        <v>single</v>
+      </c>
+      <c r="D48" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>我愿意主动对班级的规则提建议。</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I48" t="str">
+        <v>是</v>
+      </c>
+      <c r="J48" t="str">
+        <v>1</v>
+      </c>
+      <c r="K48" t="str">
+        <v>是</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N48" t="str">
+        <v>反向题：按 6−原始分 转换后计入维度</v>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B49" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C49" t="str">
+        <v>single</v>
+      </c>
+      <c r="D49" t="str">
+        <v>认知</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>上课时我会积极思考并回答老师的问题。</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I49" t="str">
+        <v>否</v>
+      </c>
+      <c r="J49" t="str">
+        <v>1</v>
+      </c>
+      <c r="K49" t="str">
+        <v>是</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B50" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C50" t="str">
+        <v>single</v>
+      </c>
+      <c r="D50" t="str">
+        <v>认知</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>我能认真订正作业里的错误。</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I50" t="str">
+        <v>否</v>
+      </c>
+      <c r="J50" t="str">
+        <v>1</v>
+      </c>
+      <c r="K50" t="str">
+        <v>是</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B51" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C51" t="str">
+        <v>single</v>
+      </c>
+      <c r="D51" t="str">
+        <v>认知</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>我相信我们这个班会越来越好。</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I51" t="str">
+        <v>否</v>
+      </c>
+      <c r="J51" t="str">
+        <v>1</v>
+      </c>
+      <c r="K51" t="str">
+        <v>是</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B52" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C52" t="str">
+        <v>single</v>
+      </c>
+      <c r="D52" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>我愿意主动举手回答问题。</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I52" t="str">
+        <v>否</v>
+      </c>
+      <c r="J52" t="str">
+        <v>1</v>
+      </c>
+      <c r="K52" t="str">
+        <v>是</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B53" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C53" t="str">
+        <v>single</v>
+      </c>
+      <c r="D53" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>我会用表情或眼神回应老师。</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I53" t="str">
+        <v>否</v>
+      </c>
+      <c r="J53" t="str">
+        <v>1</v>
+      </c>
+      <c r="K53" t="str">
+        <v>是</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B54" t="str">
+        <v>q13</v>
+      </c>
+      <c r="C54" t="str">
+        <v>single</v>
+      </c>
+      <c r="D54" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>集体任务或小组活动我都会积极参与。</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I54" t="str">
+        <v>否</v>
+      </c>
+      <c r="J54" t="str">
+        <v>1</v>
+      </c>
+      <c r="K54" t="str">
+        <v>是</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B55" t="str">
+        <v>q14</v>
+      </c>
+      <c r="C55" t="str">
+        <v>single</v>
+      </c>
+      <c r="D55" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>老师布置的事情我能很快照着做。</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I55" t="str">
+        <v>否</v>
+      </c>
+      <c r="J55" t="str">
+        <v>1</v>
+      </c>
+      <c r="K55" t="str">
+        <v>是</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B56" t="str">
+        <v>q15</v>
+      </c>
+      <c r="C56" t="str">
+        <v>single</v>
+      </c>
+      <c r="D56" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>一节课里我很少需要老师反复提醒。</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I56" t="str">
+        <v>否</v>
+      </c>
+      <c r="J56" t="str">
+        <v>1</v>
+      </c>
+      <c r="K56" t="str">
+        <v>是</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B57" t="str">
+        <v>q16</v>
+      </c>
+      <c r="C57" t="str">
+        <v>single</v>
+      </c>
+      <c r="D57" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>我会主动帮忙维护班级秩序。</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I57" t="str">
+        <v>否</v>
+      </c>
+      <c r="J57" t="str">
+        <v>1</v>
+      </c>
+      <c r="K57" t="str">
+        <v>是</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B58" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C58" t="str">
+        <v>single</v>
+      </c>
+      <c r="D58" t="str">
+        <v>认知</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>我的言行举止文明、有礼貌。</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I58" t="str">
+        <v>否</v>
+      </c>
+      <c r="J58" t="str">
+        <v>1</v>
+      </c>
+      <c r="K58" t="str">
+        <v>是</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B59" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C59" t="str">
+        <v>single</v>
+      </c>
+      <c r="D59" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>我和同学相处得融洽。</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I59" t="str">
+        <v>否</v>
+      </c>
+      <c r="J59" t="str">
+        <v>1</v>
+      </c>
+      <c r="K59" t="str">
+        <v>是</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B60" t="str">
+        <v>q19</v>
+      </c>
+      <c r="C60" t="str">
+        <v>single</v>
+      </c>
+      <c r="D60" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>同学答错时我愿意包容，不嘲笑。</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I60" t="str">
+        <v>否</v>
+      </c>
+      <c r="J60" t="str">
+        <v>1</v>
+      </c>
+      <c r="K60" t="str">
+        <v>是</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B61" t="str">
+        <v>q20</v>
+      </c>
+      <c r="C61" t="str">
+        <v>single</v>
+      </c>
+      <c r="D61" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>同学学习遇到困难时我愿意帮忙。</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I61" t="str">
+        <v>否</v>
+      </c>
+      <c r="J61" t="str">
+        <v>1</v>
+      </c>
+      <c r="K61" t="str">
+        <v>是</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B62" t="str">
+        <v>q21</v>
+      </c>
+      <c r="C62" t="str">
+        <v>single</v>
+      </c>
+      <c r="D62" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>别人批评我时，我愿意听并回应。</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I62" t="str">
+        <v>是</v>
+      </c>
+      <c r="J62" t="str">
+        <v>1</v>
+      </c>
+      <c r="K62" t="str">
+        <v>是</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N62" t="str">
+        <v>反向题：按 6−原始分 转换后计入维度</v>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B63" t="str">
+        <v>q22</v>
+      </c>
+      <c r="C63" t="str">
+        <v>single</v>
+      </c>
+      <c r="D63" t="str">
+        <v>认知</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>我愿意主动和老师交流。</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I63" t="str">
+        <v>否</v>
+      </c>
+      <c r="J63" t="str">
+        <v>1</v>
+      </c>
+      <c r="K63" t="str">
+        <v>是</v>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B64" t="str">
+        <v>q23</v>
+      </c>
+      <c r="C64" t="str">
+        <v>single</v>
+      </c>
+      <c r="D64" t="str">
+        <v>环境</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>我对待学习的态度是认真的。</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I64" t="str">
+        <v>是</v>
+      </c>
+      <c r="J64" t="str">
+        <v>1</v>
+      </c>
+      <c r="K64" t="str">
+        <v>是</v>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N64" t="str">
+        <v>反向题：按 6−原始分 转换后计入维度（环境为筛查层）</v>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B65" t="str">
+        <v>q24</v>
+      </c>
+      <c r="C65" t="str">
+        <v>single</v>
+      </c>
+      <c r="D65" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>我精神状态饱满，上课有精神。</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I65" t="str">
+        <v>否</v>
+      </c>
+      <c r="J65" t="str">
+        <v>1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>是</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B66" t="str">
+        <v>q25</v>
+      </c>
+      <c r="C66" t="str">
+        <v>single</v>
+      </c>
+      <c r="D66" t="str">
+        <v>环境</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>遇到困难时我愿意求助，而不是放弃。</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I66" t="str">
+        <v>否</v>
+      </c>
+      <c r="J66" t="str">
+        <v>1</v>
+      </c>
+      <c r="K66" t="str">
+        <v>是</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B67" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C67" t="str">
+        <v>single</v>
+      </c>
+      <c r="D67" t="str">
+        <v>情感</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>情感：①面部表情（放松/平静/紧绷）②整体情绪温度</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>CS_OPT_01</v>
+      </c>
+      <c r="I67" t="str">
+        <v>否</v>
+      </c>
+      <c r="J67" t="str">
+        <v>1</v>
+      </c>
+      <c r="K67" t="str">
+        <v>是</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N67" t="str">
+        <v>走进教室第一感觉即最真实数据</v>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B68" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C68" t="str">
+        <v>single</v>
+      </c>
+      <c r="D68" t="str">
+        <v>认知</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>认知：①口头指代（我们班/这个班）②规则讨论频次</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>CS_OPT_01</v>
+      </c>
+      <c r="I68" t="str">
+        <v>否</v>
+      </c>
+      <c r="J68" t="str">
+        <v>1</v>
+      </c>
+      <c r="K68" t="str">
+        <v>是</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N68" t="str">
+        <v>「我们班」占比高=认同高</v>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B69" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C69" t="str">
+        <v>single</v>
+      </c>
+      <c r="D69" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>行为：①课前状态②指令响应速度③自习纪律</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v>CS_OPT_01</v>
+      </c>
+      <c r="I69" t="str">
+        <v>否</v>
+      </c>
+      <c r="J69" t="str">
+        <v>1</v>
+      </c>
+      <c r="K69" t="str">
+        <v>是</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N69" t="str">
+        <v>非检查，是感受</v>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B70" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C70" t="str">
+        <v>single</v>
+      </c>
+      <c r="D70" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>关系：①同伴互动（互助/冲突）②师生互动姿态</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>CS_OPT_01</v>
+      </c>
+      <c r="I70" t="str">
+        <v>否</v>
+      </c>
+      <c r="J70" t="str">
+        <v>1</v>
+      </c>
+      <c r="K70" t="str">
+        <v>是</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N70" t="str">
+        <v>观察小圈子与落单者</v>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B71" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C71" t="str">
+        <v>single</v>
+      </c>
+      <c r="D71" t="str">
+        <v>环境</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>环境：①整洁度②绿植/布置（仅筛查，不计入能量场综合均值）</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>CS_OPT_01</v>
+      </c>
+      <c r="I71" t="str">
+        <v>否</v>
+      </c>
+      <c r="J71" t="str">
+        <v>1</v>
+      </c>
+      <c r="K71" t="str">
+        <v>是</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B72" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C72" t="str">
+        <v>single</v>
+      </c>
+      <c r="D72" t="str">
+        <v>情感</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>情感：1分=面无表情/趴桌比例&gt;30%；3分=部分学生主动参与；5分=集体自发的笑声、击掌</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>CS_OPT_02</v>
+      </c>
+      <c r="I72" t="str">
+        <v>否</v>
+      </c>
+      <c r="J72" t="str">
+        <v>1</v>
+      </c>
+      <c r="K72" t="str">
+        <v>是</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B73" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C73" t="str">
+        <v>single</v>
+      </c>
+      <c r="D73" t="str">
+        <v>认知</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>认知：1分=「这个班」频率高、外归因；3分=「我们班」与「这个班」并存；5分=「我们班」为主、主动为班级归因</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v>CS_OPT_02</v>
+      </c>
+      <c r="I73" t="str">
+        <v>否</v>
+      </c>
+      <c r="J73" t="str">
+        <v>1</v>
+      </c>
+      <c r="K73" t="str">
+        <v>是</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B74" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C74" t="str">
+        <v>single</v>
+      </c>
+      <c r="D74" t="str">
+        <v>行为</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>行为：1分=需反复提醒、抄作业现象多；3分=基本按时按质；5分=主动举手、主动完成</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>CS_OPT_02</v>
+      </c>
+      <c r="I74" t="str">
+        <v>否</v>
+      </c>
+      <c r="J74" t="str">
+        <v>1</v>
+      </c>
+      <c r="K74" t="str">
+        <v>是</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B75" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C75" t="str">
+        <v>single</v>
+      </c>
+      <c r="D75" t="str">
+        <v>关系</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>关系：1分=独来独往比例高、冲突多；3分=小圈子明显但稳定；5分=课间合作游戏、主动找老师</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v>CS_OPT_02</v>
+      </c>
+      <c r="I75" t="str">
+        <v>否</v>
+      </c>
+      <c r="J75" t="str">
+        <v>1</v>
+      </c>
+      <c r="K75" t="str">
+        <v>是</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B76" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C76" t="str">
+        <v>single</v>
+      </c>
+      <c r="D76" t="str">
+        <v>环境</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>环境：1分=桌椅乱、墙面陈旧、绿植枯萎；3分=基本整洁、布置常规；5分=教室有「家」的感觉、学生主动维护（筛查层）</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v>CS_OPT_02</v>
+      </c>
+      <c r="I76" t="str">
+        <v>否</v>
+      </c>
+      <c r="J76" t="str">
+        <v>1</v>
+      </c>
+      <c r="K76" t="str">
+        <v>是</v>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="B77" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C77" t="str">
+        <v>single</v>
+      </c>
+      <c r="D77" t="str">
+        <v>风险等级</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>A级·安全危机：自伤/伤他念头或行为、严重家庭变故、性侵线索</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I77" t="str">
+        <v>否</v>
+      </c>
+      <c r="J77" t="str">
+        <v>1</v>
+      </c>
+      <c r="K77" t="str">
+        <v>是</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N77" t="str">
+        <v>量化指标：出现自伤工具持有、攻击性威胁言论、躯体化反应；响应：24小时内学校+公安+心理转介</v>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="B78" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C78" t="str">
+        <v>single</v>
+      </c>
+      <c r="D78" t="str">
+        <v>风险等级</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>B级·高风险：持续情绪低落≥2周、自伤意念、家庭剧变、行为冲突频发(周均≥5次)</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I78" t="str">
+        <v>否</v>
+      </c>
+      <c r="J78" t="str">
+        <v>1</v>
+      </c>
+      <c r="K78" t="str">
+        <v>是</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N78" t="str">
+        <v>量化指标：周均≥5次冲突、确诊多动/自闭等行为障碍；响应：48小时评估、家长面谈、专业转介</v>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="B79" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C79" t="str">
+        <v>single</v>
+      </c>
+      <c r="D79" t="str">
+        <v>风险等级</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>C级·中度困扰：1-2周情绪低落、回避社交、成绩骤降、外向攻击</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I79" t="str">
+        <v>否</v>
+      </c>
+      <c r="J79" t="str">
+        <v>1</v>
+      </c>
+      <c r="K79" t="str">
+        <v>是</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N79" t="str">
+        <v>量化指标：破坏公物、欺凌行为、对抗权威；响应：1周内班主任+心理教师介入</v>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="B80" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C80" t="str">
+        <v>single</v>
+      </c>
+      <c r="D80" t="str">
+        <v>风险等级</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>D级·轻度关注：多动倾向、注意分散、偶发冲突、课堂干扰</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I80" t="str">
+        <v>否</v>
+      </c>
+      <c r="J80" t="str">
+        <v>1</v>
+      </c>
+      <c r="K80" t="str">
+        <v>是</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N80" t="str">
+        <v>量化指标：多动倾向、注意分散、偶发冲突(可控)；响应：1个月内家校沟通、班级内支持</v>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="B81" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C81" t="str">
+        <v>single</v>
+      </c>
+      <c r="D81" t="str">
+        <v>风险等级</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>E级·健康观察：适应良好、偶有情绪起伏、内向困扰</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I81" t="str">
+        <v>否</v>
+      </c>
+      <c r="J81" t="str">
+        <v>1</v>
+      </c>
+      <c r="K81" t="str">
+        <v>是</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N81" t="str">
+        <v>量化指标：持续抑郁/焦虑倾向、社交回避；响应：常规关注、月度追踪</v>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B82" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C82" t="str">
+        <v>single</v>
+      </c>
+      <c r="D82" t="str">
+        <v>通用</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>通用·画面布局：过于偏角/挤压边缘；极空或溢出；主体压底</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I82" t="str">
+        <v>否</v>
+      </c>
+      <c r="J82" t="str">
+        <v>1</v>
+      </c>
+      <c r="K82" t="str">
+        <v>是</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N82" t="str">
+        <v>可能指向：边缘化/不安全感；或控制欲/冲动（风险：黄）</v>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B83" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C83" t="str">
+        <v>single</v>
+      </c>
+      <c r="D83" t="str">
+        <v>通用</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v>通用·大小比例：单一物体异常巨大/渺小</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I83" t="str">
+        <v>否</v>
+      </c>
+      <c r="J83" t="str">
+        <v>1</v>
+      </c>
+      <c r="K83" t="str">
+        <v>是</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N83" t="str">
+        <v>可能指向：自我膨胀/控制欲；或自卑/被压迫（风险：橙）</v>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B84" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C84" t="str">
+        <v>single</v>
+      </c>
+      <c r="D84" t="str">
+        <v>通用</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v>通用·透视/空间：漂浮无地面线；关系严重错乱</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I84" t="str">
+        <v>否</v>
+      </c>
+      <c r="J84" t="str">
+        <v>1</v>
+      </c>
+      <c r="K84" t="str">
+        <v>是</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N84" t="str">
+        <v>可能指向：现实感薄弱、自我界限模糊（风险：红）</v>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B85" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C85" t="str">
+        <v>single</v>
+      </c>
+      <c r="D85" t="str">
+        <v>通用</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>通用·线条质量：断续颤抖；用力刻破纸；生硬直线</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I85" t="str">
+        <v>否</v>
+      </c>
+      <c r="J85" t="str">
+        <v>1</v>
+      </c>
+      <c r="K85" t="str">
+        <v>是</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N85" t="str">
+        <v>可能指向：焦虑/控制/情感隔离（风险：黄）</v>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B86" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C86" t="str">
+        <v>single</v>
+      </c>
+      <c r="D86" t="str">
+        <v>通用</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>通用·阴影/涂黑：大面积涂黑；主体被重阴影裹</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I86" t="str">
+        <v>否</v>
+      </c>
+      <c r="J86" t="str">
+        <v>1</v>
+      </c>
+      <c r="K86" t="str">
+        <v>是</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N86" t="str">
+        <v>可能指向：抑郁、内疚、被压迫（风险：橙）</v>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B87" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C87" t="str">
+        <v>single</v>
+      </c>
+      <c r="D87" t="str">
+        <v>通用</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>通用·省略/缺失：人无脸/手/脚、房无门无窗、树无根</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I87" t="str">
+        <v>否</v>
+      </c>
+      <c r="J87" t="str">
+        <v>1</v>
+      </c>
+      <c r="K87" t="str">
+        <v>是</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N87" t="str">
+        <v>可能指向：回避、自我界限、行动力缺失（风险：橙）</v>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B88" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C88" t="str">
+        <v>single</v>
+      </c>
+      <c r="D88" t="str">
+        <v>通用</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>通用·附加物：诡异生物、防御工事、武器、血迹</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I88" t="str">
+        <v>否</v>
+      </c>
+      <c r="J88" t="str">
+        <v>1</v>
+      </c>
+      <c r="K88" t="str">
+        <v>是</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N88" t="str">
+        <v>依内容判断（见红旗清单）（风险：红）</v>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B89" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C89" t="str">
+        <v>single</v>
+      </c>
+      <c r="D89" t="str">
+        <v>HTP·房</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>HTP·房·门/窗：无门/重锁/铁栏；无窗</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I89" t="str">
+        <v>否</v>
+      </c>
+      <c r="J89" t="str">
+        <v>1</v>
+      </c>
+      <c r="K89" t="str">
+        <v>是</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N89" t="str">
+        <v>可能指向：社交封闭、防御过度、不安全感（风险：橙）</v>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B90" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C90" t="str">
+        <v>single</v>
+      </c>
+      <c r="D90" t="str">
+        <v>HTP·树</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>HTP·树·树根/干：无根/根断；枯无皮/裂/虫洞/砍断</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I90" t="str">
+        <v>否</v>
+      </c>
+      <c r="J90" t="str">
+        <v>1</v>
+      </c>
+      <c r="K90" t="str">
+        <v>是</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N90" t="str">
+        <v>可能指向：生命力受损/创伤/自我脆弱（风险：红）</v>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B91" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C91" t="str">
+        <v>single</v>
+      </c>
+      <c r="D91" t="str">
+        <v>HTP·人</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>HTP·人·眼/臂/脸：眼被挖空；无臂；无脸</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I91" t="str">
+        <v>否</v>
+      </c>
+      <c r="J91" t="str">
+        <v>1</v>
+      </c>
+      <c r="K91" t="str">
+        <v>是</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N91" t="str">
+        <v>可能指向：被监视感/行动力缺失/认同模糊（风险：红/橙）</v>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B92" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C92" t="str">
+        <v>single</v>
+      </c>
+      <c r="D92" t="str">
+        <v>雨中人</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>雨中人·防护物：无伞无衣直接暴露；伞破失效</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I92" t="str">
+        <v>否</v>
+      </c>
+      <c r="J92" t="str">
+        <v>1</v>
+      </c>
+      <c r="K92" t="str">
+        <v>是</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N92" t="str">
+        <v>可能指向：缺乏应对资源、无助（重点）（风险：红）</v>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B93" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C93" t="str">
+        <v>single</v>
+      </c>
+      <c r="D93" t="str">
+        <v>雨中人</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>雨中人·人物状态：被雨压弯/蜷缩/跌倒水洼</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I93" t="str">
+        <v>否</v>
+      </c>
+      <c r="J93" t="str">
+        <v>1</v>
+      </c>
+      <c r="K93" t="str">
+        <v>是</v>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N93" t="str">
+        <v>可能指向：被压垮、无力、抑郁倾向（风险：红）</v>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B94" t="str">
+        <v>q13</v>
+      </c>
+      <c r="C94" t="str">
+        <v>single</v>
+      </c>
+      <c r="D94" t="str">
+        <v>雨中人</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>雨中人·积极资源：有效雨伞/稳固房屋/他人共撑/彩虹</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I94" t="str">
+        <v>否</v>
+      </c>
+      <c r="J94" t="str">
+        <v>1</v>
+      </c>
+      <c r="K94" t="str">
+        <v>是</v>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N94" t="str">
+        <v>保护性因素，风险相对降低（风险：绿）</v>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B95" t="str">
+        <v>q14</v>
+      </c>
+      <c r="C95" t="str">
+        <v>single</v>
+      </c>
+      <c r="D95" t="str">
+        <v>树木画</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>树木画·树干纹理：皮剥落/裂/虫洞/绳捆</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I95" t="str">
+        <v>否</v>
+      </c>
+      <c r="J95" t="str">
+        <v>1</v>
+      </c>
+      <c r="K95" t="str">
+        <v>是</v>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N95" t="str">
+        <v>可能指向：创伤印记/受束缚/自我受损（风险：红）</v>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B96" t="str">
+        <v>q15</v>
+      </c>
+      <c r="C96" t="str">
+        <v>single</v>
+      </c>
+      <c r="D96" t="str">
+        <v>树木画</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>树木画·气象附加：风暴劈树/连根拔起/火焚</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I96" t="str">
+        <v>否</v>
+      </c>
+      <c r="J96" t="str">
+        <v>1</v>
+      </c>
+      <c r="K96" t="str">
+        <v>是</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N96" t="str">
+        <v>可能指向：重大危机/创伤/毁灭感（风险：红）</v>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B97" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C97" t="str">
+        <v>single</v>
+      </c>
+      <c r="D97" t="str">
+        <v>家庭背景</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>家庭背景问1：孩子平时更喜欢找谁？（了解主要依恋对象）</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I97" t="str">
+        <v>否</v>
+      </c>
+      <c r="J97" t="str">
+        <v>1</v>
+      </c>
+      <c r="K97" t="str">
+        <v>是</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N97" t="str">
+        <v>家访/家长会自然对话收集，切忌审问</v>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B98" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C98" t="str">
+        <v>single</v>
+      </c>
+      <c r="D98" t="str">
+        <v>家庭背景</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>家庭背景问2：孩子情绪不好时，你们通常怎么处理？（照料者回应模式）</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I98" t="str">
+        <v>否</v>
+      </c>
+      <c r="J98" t="str">
+        <v>1</v>
+      </c>
+      <c r="K98" t="str">
+        <v>是</v>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N98" t="str">
+        <v>记录回应模式一致性</v>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B99" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C99" t="str">
+        <v>single</v>
+      </c>
+      <c r="D99" t="str">
+        <v>家庭背景</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>家庭背景问3：孩子在家会主动说学校的事情吗？（家庭沟通开放度）</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I99" t="str">
+        <v>否</v>
+      </c>
+      <c r="J99" t="str">
+        <v>1</v>
+      </c>
+      <c r="K99" t="str">
+        <v>是</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N99" t="str">
+        <v>评估沟通开放度</v>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B100" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C100" t="str">
+        <v>single</v>
+      </c>
+      <c r="D100" t="str">
+        <v>家庭背景</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>家庭背景问4：有没有什么“变化”让孩子比较难适应？（创伤/重大变化）</v>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I100" t="str">
+        <v>否</v>
+      </c>
+      <c r="J100" t="str">
+        <v>1</v>
+      </c>
+      <c r="K100" t="str">
+        <v>是</v>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N100" t="str">
+        <v>识别转型/创伤信号</v>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B101" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C101" t="str">
+        <v>single</v>
+      </c>
+      <c r="D101" t="str">
+        <v>家庭背景</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>家庭背景问5：孩子有没有特别依赖或回避的物品/场所/人？（依恋信号物）</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I101" t="str">
+        <v>否</v>
+      </c>
+      <c r="J101" t="str">
+        <v>1</v>
+      </c>
+      <c r="K101" t="str">
+        <v>是</v>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N101" t="str">
+        <v>记录依恋信号物</v>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B102" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C102" t="str">
+        <v>single</v>
+      </c>
+      <c r="D102" t="str">
+        <v>依恋类型</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>安全型：主动靠近教师寻求安慰；有稳定朋友圈；愿意倾诉</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I102" t="str">
+        <v>否</v>
+      </c>
+      <c r="J102" t="str">
+        <v>1</v>
+      </c>
+      <c r="K102" t="str">
+        <v>是</v>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N102" t="str">
+        <v>全班通用：建设安全基地（可预期、在场）</v>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B103" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C103" t="str">
+        <v>single</v>
+      </c>
+      <c r="D103" t="str">
+        <v>依恋类型</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>A型·回避：不要求情绪表达；用共同任务/并行活动切入；小任务委托</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I103" t="str">
+        <v>否</v>
+      </c>
+      <c r="J103" t="str">
+        <v>1</v>
+      </c>
+      <c r="K103" t="str">
+        <v>是</v>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N103" t="str">
+        <v>无压力关系建立，从认知切入，不逼情绪暴露</v>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B104" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C104" t="str">
+        <v>single</v>
+      </c>
+      <c r="D104" t="str">
+        <v>依恋类型</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>C型·焦虑-矛盾：最需要一致性；结构化安抚+情绪验证+渐进分离仪式</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I104" t="str">
+        <v>否</v>
+      </c>
+      <c r="J104" t="str">
+        <v>1</v>
+      </c>
+      <c r="K104" t="str">
+        <v>是</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N104" t="str">
+        <v>教师反应可预期，陪伴不急于消除情绪</v>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B105" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C105" t="str">
+        <v>single</v>
+      </c>
+      <c r="D105" t="str">
+        <v>依恋类型</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v>D型·混乱：提供稳定而非解决创伤；保持预测性；允许不信任；危机预案</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I105" t="str">
+        <v>否</v>
+      </c>
+      <c r="J105" t="str">
+        <v>1</v>
+      </c>
+      <c r="K105" t="str">
+        <v>是</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N105" t="str">
+        <v>必要时立即联动专业支持，制定个性危机流程</v>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B106" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C106" t="str">
+        <v>single</v>
+      </c>
+      <c r="D106" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v>观察·情绪稳定性：情绪起伏是否平缓可控</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I106" t="str">
+        <v>否</v>
+      </c>
+      <c r="J106" t="str">
+        <v>1</v>
+      </c>
+      <c r="K106" t="str">
+        <v>是</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B107" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C107" t="str">
+        <v>single</v>
+      </c>
+      <c r="D107" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v>观察·社交连接：与同伴的互动质量与频率</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I107" t="str">
+        <v>否</v>
+      </c>
+      <c r="J107" t="str">
+        <v>1</v>
+      </c>
+      <c r="K107" t="str">
+        <v>是</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B108" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C108" t="str">
+        <v>single</v>
+      </c>
+      <c r="D108" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>观察·分离反应：与主要照料者分离时的反应</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I108" t="str">
+        <v>否</v>
+      </c>
+      <c r="J108" t="str">
+        <v>1</v>
+      </c>
+      <c r="K108" t="str">
+        <v>是</v>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B109" t="str">
+        <v>q13</v>
+      </c>
+      <c r="C109" t="str">
+        <v>single</v>
+      </c>
+      <c r="D109" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>观察·求助行为：遇到困难时是否会主动求助</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I109" t="str">
+        <v>否</v>
+      </c>
+      <c r="J109" t="str">
+        <v>1</v>
+      </c>
+      <c r="K109" t="str">
+        <v>是</v>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B110" t="str">
+        <v>q14</v>
+      </c>
+      <c r="C110" t="str">
+        <v>single</v>
+      </c>
+      <c r="D110" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>观察·规则回应：对班级规则与指令的回应方式</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I110" t="str">
+        <v>否</v>
+      </c>
+      <c r="J110" t="str">
+        <v>1</v>
+      </c>
+      <c r="K110" t="str">
+        <v>是</v>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B111" t="str">
+        <v>q15</v>
+      </c>
+      <c r="C111" t="str">
+        <v>single</v>
+      </c>
+      <c r="D111" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>观察·任务投入：对学习任务的投入程度</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I111" t="str">
+        <v>否</v>
+      </c>
+      <c r="J111" t="str">
+        <v>1</v>
+      </c>
+      <c r="K111" t="str">
+        <v>是</v>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B112" t="str">
+        <v>q16</v>
+      </c>
+      <c r="C112" t="str">
+        <v>single</v>
+      </c>
+      <c r="D112" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>观察·依恋信号物：是否存在特别依赖或回避的物品/场所/人</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="I112" t="str">
+        <v>否</v>
+      </c>
+      <c r="J112" t="str">
+        <v>1</v>
+      </c>
+      <c r="K112" t="str">
+        <v>是</v>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="B113" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C113" t="str">
+        <v>single</v>
+      </c>
+      <c r="D113" t="str">
+        <v>个案类型</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v>【成功型】能力高×意愿高：表现好，可能隐藏风险（倦怠/骄傲）</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I113" t="str">
+        <v>否</v>
+      </c>
+      <c r="J113" t="str">
+        <v>1</v>
+      </c>
+      <c r="K113" t="str">
+        <v>是</v>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N113" t="str">
+        <v>策略：激发更高目标，防止倦怠/骄傲</v>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="B114" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C114" t="str">
+        <v>single</v>
+      </c>
+      <c r="D114" t="str">
+        <v>个案类型</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>【挫折型】能力高×意愿低：会做但不愿做，可能反复失败/被否定</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I114" t="str">
+        <v>否</v>
+      </c>
+      <c r="J114" t="str">
+        <v>1</v>
+      </c>
+      <c r="K114" t="str">
+        <v>是</v>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N114" t="str">
+        <v>策略：拆解目标、重建小成功</v>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="B115" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C115" t="str">
+        <v>single</v>
+      </c>
+      <c r="D115" t="str">
+        <v>个案类型</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v>【对抗型】能力低×意愿高：不会做但嘴硬/用行为表达不满</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I115" t="str">
+        <v>否</v>
+      </c>
+      <c r="J115" t="str">
+        <v>1</v>
+      </c>
+      <c r="K115" t="str">
+        <v>是</v>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N115" t="str">
+        <v>策略：先建立关系、再处理行为</v>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="B116" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C116" t="str">
+        <v>single</v>
+      </c>
+      <c r="D116" t="str">
+        <v>个案类型</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v>【放弃型】能力低×意愿低：不会做也不想做，长期受挫/被边缘化</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I116" t="str">
+        <v>否</v>
+      </c>
+      <c r="J116" t="str">
+        <v>1</v>
+      </c>
+      <c r="K116" t="str">
+        <v>是</v>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N116" t="str">
+        <v>策略：先看见人、再处理学习</v>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B117" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C117" t="str">
+        <v>single</v>
+      </c>
+      <c r="D117" t="str">
+        <v>情绪症状</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v>情绪症状：情绪低落、焦虑、恐惧、躯体不适</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I117" t="str">
+        <v>否</v>
+      </c>
+      <c r="J117" t="str">
+        <v>1</v>
+      </c>
+      <c r="K117" t="str">
+        <v>是</v>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N117" t="str">
+        <v>教师版评定；汇总看是否达临床区间</v>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B118" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C118" t="str">
+        <v>single</v>
+      </c>
+      <c r="D118" t="str">
+        <v>品行问题</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v>品行问题：攻击、说谎、偷拿、违抗</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I118" t="str">
+        <v>否</v>
+      </c>
+      <c r="J118" t="str">
+        <v>1</v>
+      </c>
+      <c r="K118" t="str">
+        <v>是</v>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N118" t="str">
+        <v>结合日常观察</v>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B119" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C119" t="str">
+        <v>single</v>
+      </c>
+      <c r="D119" t="str">
+        <v>多动注意</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v>多动/注意：坐不住、易分心、冲动</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I119" t="str">
+        <v>否</v>
+      </c>
+      <c r="J119" t="str">
+        <v>1</v>
+      </c>
+      <c r="K119" t="str">
+        <v>是</v>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N119" t="str">
+        <v>注意与环境干扰区分</v>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B120" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C120" t="str">
+        <v>single</v>
+      </c>
+      <c r="D120" t="str">
+        <v>同伴交往</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v>同伴交往：孤独、被排挤、少朋友</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I120" t="str">
+        <v>否</v>
+      </c>
+      <c r="J120" t="str">
+        <v>1</v>
+      </c>
+      <c r="K120" t="str">
+        <v>是</v>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N120" t="str">
+        <v>关注社交回避</v>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B121" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C121" t="str">
+        <v>single</v>
+      </c>
+      <c r="D121" t="str">
+        <v>亲社会行为</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v>亲社会行为：乐于助人、体谅他人</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I121" t="str">
+        <v>否</v>
+      </c>
+      <c r="J121" t="str">
+        <v>1</v>
+      </c>
+      <c r="K121" t="str">
+        <v>是</v>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N121" t="str">
+        <v>保护性因素</v>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P121"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2690,13 +7836,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FREQ_5</v>
+        <v>CS_OPT_01</v>
       </c>
       <c r="B7" t="str">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>几乎没有</v>
+        <v>需关注</v>
       </c>
       <c r="D7" t="str">
         <v>1</v>
@@ -2704,13 +7850,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FREQ_5</v>
+        <v>CS_OPT_01</v>
       </c>
       <c r="B8" t="str">
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>很少</v>
+        <v>一般</v>
       </c>
       <c r="D8" t="str">
         <v>2</v>
@@ -2718,13 +7864,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>FREQ_5</v>
+        <v>CS_OPT_01</v>
       </c>
       <c r="B9" t="str">
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>有时</v>
+        <v>良好</v>
       </c>
       <c r="D9" t="str">
         <v>3</v>
@@ -2732,42 +7878,126 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>FREQ_5</v>
+        <v>CS_OPT_02</v>
       </c>
       <c r="B10" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>经常</v>
+        <v>1分·低能量</v>
       </c>
       <c r="D10" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FREQ_5</v>
+        <v>CS_OPT_02</v>
       </c>
       <c r="B11" t="str">
+        <v>2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>3分·中能量</v>
+      </c>
+      <c r="D11" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_OPT_02</v>
+      </c>
+      <c r="B12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>5分·高能量</v>
+      </c>
+      <c r="D12" t="str">
         <v>5</v>
       </c>
-      <c r="C11" t="str">
-        <v>几乎每天</v>
-      </c>
-      <c r="D11" t="str">
-        <v>5</v>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="B13" t="str">
+        <v>1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>否</v>
+      </c>
+      <c r="D13" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2</v>
+      </c>
+      <c r="C14" t="str">
+        <v>是</v>
+      </c>
+      <c r="D14" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="B15" t="str">
+        <v>1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>未观察到</v>
+      </c>
+      <c r="D15" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>有时出现</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_OPT_03</v>
+      </c>
+      <c r="B17" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>明显出现</v>
+      </c>
+      <c r="D17" t="str">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2812,7 +8042,7 @@
         <v>CS_S1D1</v>
       </c>
       <c r="C2" t="str">
-        <v>目标系统</v>
+        <v>关系系统</v>
       </c>
       <c r="D2" t="str">
         <v>q1,q2,q3</v>
@@ -2824,13 +8054,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>目标系统维度</v>
+        <v>同伴互助、氛围温暖、弱势学生不被孤立</v>
       </c>
       <c r="H2" t="str">
-        <v>目标未被学生理解或未转化为可观察里程碑</v>
+        <v>关系稳定，学生被听见、同伴互助充分</v>
       </c>
       <c r="I2" t="str">
-        <v>目标清晰且已落地</v>
+        <v>冲突难以修复，存在被孤立或欺负的学生</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -2847,7 +8077,7 @@
         <v>CS_S1D2</v>
       </c>
       <c r="C3" t="str">
-        <v>权力系统</v>
+        <v>组织系统</v>
       </c>
       <c r="D3" t="str">
         <v>q4,q5,q6</v>
@@ -2859,13 +8089,13 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>权力系统维度</v>
+        <v>班委服务意识、参与渠道、无人被边缘化</v>
       </c>
       <c r="H3" t="str">
-        <v>岗位职责不清，事务集中在教师身上</v>
+        <v>岗位职责清晰，事务分散自主运转</v>
       </c>
       <c r="I3" t="str">
-        <v>学生分工稳定运转</v>
+        <v>班委形同虚设，事务集中在教师身上</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -2882,7 +8112,7 @@
         <v>CS_S1D3</v>
       </c>
       <c r="C4" t="str">
-        <v>情感系统</v>
+        <v>规范系统</v>
       </c>
       <c r="D4" t="str">
         <v>q7,q8,q9</v>
@@ -2894,13 +8124,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>情感系统维度</v>
+        <v>规则认同、执行一致公平、规则有弹性</v>
       </c>
       <c r="H4" t="str">
-        <v>活动脱离学生真实需要且缺少复盘</v>
+        <v>规则被理解并一致执行，秩序可自主恢复</v>
       </c>
       <c r="I4" t="str">
-        <v>活动有回应、有复盘</v>
+        <v>规则悬空、督导标准不一，混乱后难以恢复</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -2917,7 +8147,7 @@
         <v>CS_S1D4</v>
       </c>
       <c r="C5" t="str">
-        <v>规范系统</v>
+        <v>目标系统</v>
       </c>
       <c r="D5" t="str">
         <v>q10,q11,q12</v>
@@ -2929,13 +8159,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>规范系统维度</v>
+        <v>学习目标与动力、班级共同目标、目标凝聚力</v>
       </c>
       <c r="H5" t="str">
-        <v>规则停留在墙上，混乱后难以恢复</v>
+        <v>目标清晰并转化为可观察里程碑</v>
       </c>
       <c r="I5" t="str">
-        <v>环境与规则支持秩序</v>
+        <v>目标缺位、空泛，努力无方向</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -2952,7 +8182,7 @@
         <v>CS_S1D5</v>
       </c>
       <c r="C6" t="str">
-        <v>关系系统</v>
+        <v>情感系统</v>
       </c>
       <c r="D6" t="str">
         <v>q13,q14,q15</v>
@@ -2964,13 +8194,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>关系系统维度</v>
+        <v>上学意愿、求助行为、集体荣誉感</v>
       </c>
       <c r="H6" t="str">
-        <v>冲突难以修复，缺少同伴互助</v>
+        <v>归属感强，学生愿意来学校、遇到问题会求助</v>
       </c>
       <c r="I6" t="str">
-        <v>关系稳定，学生被听见</v>
+        <v>氛围负向，个体情绪失接、集体无温度</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -2987,10 +8217,10 @@
         <v>CS_S2D1</v>
       </c>
       <c r="C7" t="str">
-        <v>秩序能量</v>
+        <v>情感</v>
       </c>
       <c r="D7" t="str">
-        <v>q1,q2</v>
+        <v>q1,q2,q3,q4,q5</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -2999,13 +8229,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>秩序能量维度</v>
+        <v>课堂氛围、师生情绪体验（情感维度）</v>
       </c>
       <c r="H7" t="str">
-        <v>秩序需要教师持续在场维持</v>
+        <v>氛围积极，师生情绪体验良好</v>
       </c>
       <c r="I7" t="str">
-        <v>秩序可自主维持</v>
+        <v>氛围压抑，教师压力大、被接纳感低</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -3022,10 +8252,10 @@
         <v>CS_S2D2</v>
       </c>
       <c r="C8" t="str">
-        <v>学习能量</v>
+        <v>认知</v>
       </c>
       <c r="D8" t="str">
-        <v>q3,q4</v>
+        <v>q6,q7,q8,q9,q10</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -3034,13 +8264,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>学习能量维度</v>
+        <v>集体荣誉感、规则建议、思考回答、学习信心（认知维度）</v>
       </c>
       <c r="H8" t="str">
-        <v>学习投入依赖外部推动</v>
+        <v>班级认同高，思考与订正投入</v>
       </c>
       <c r="I8" t="str">
-        <v>学习氛围自发</v>
+        <v>认同感低，学习投入依赖外部推动</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -3057,10 +8287,10 @@
         <v>CS_S2D3</v>
       </c>
       <c r="C9" t="str">
-        <v>联结能量</v>
+        <v>行为</v>
       </c>
       <c r="D9" t="str">
-        <v>q5,q6</v>
+        <v>q11,q12,q13,q14,q15,q16,q17</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -3069,13 +8299,13 @@
         <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v>联结能量维度</v>
+        <v>举手提问、指令响应、任务参与、秩序维护（行为维度）</v>
       </c>
       <c r="H9" t="str">
-        <v>学生之间缺少正向联结</v>
+        <v>行为规范自主，参与度高</v>
       </c>
       <c r="I9" t="str">
-        <v>同伴联结紧密</v>
+        <v>需反复提醒，秩序依赖教师在场</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -3086,16 +8316,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CS_S3</v>
+        <v>CS_S2</v>
       </c>
       <c r="B10" t="str">
-        <v>CS_S3D1</v>
+        <v>CS_S2D4</v>
       </c>
       <c r="C10" t="str">
-        <v>截断信号</v>
+        <v>关系</v>
       </c>
       <c r="D10" t="str">
-        <v>q1,q2,q3,q4</v>
+        <v>q18,q19,q20,q21,q22</v>
       </c>
       <c r="E10" t="str">
         <v>mean</v>
@@ -3104,13 +8334,13 @@
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>四类截断信号的总体频率，越高越接近爆发临界</v>
+        <v>同学相处、互助、师生交流（关系维度）</v>
       </c>
       <c r="H10" t="str">
-        <v>信号频繁被截断，堰塞湖蓄积风险高</v>
+        <v>同伴联结紧密，愿意与教师交流</v>
       </c>
       <c r="I10" t="str">
-        <v>信号有正常表达出口</v>
+        <v>学生之间缺少正向联结</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -3121,16 +8351,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CS_S4</v>
+        <v>CS_S2</v>
       </c>
       <c r="B11" t="str">
-        <v>CS_S4D1</v>
+        <v>CS_S2D5</v>
       </c>
       <c r="C11" t="str">
-        <v>组织分工</v>
+        <v>环境</v>
       </c>
       <c r="D11" t="str">
-        <v>q1,q2,q6</v>
+        <v>q23,q24,q25</v>
       </c>
       <c r="E11" t="str">
         <v>mean</v>
@@ -3139,13 +8369,13 @@
         <v>1</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>学习态度、精神状态（环境维度·筛查层，不计入五维综合均值，单独报告）</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>状态饱满、求助而非放弃</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>状态低迷，需关注个体支持</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -3156,16 +8386,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_S4</v>
+        <v>CS_S3</v>
       </c>
       <c r="B12" t="str">
-        <v>CS_S4D2</v>
+        <v>CS_S3D1</v>
       </c>
       <c r="C12" t="str">
-        <v>秩序系统</v>
+        <v>情感</v>
       </c>
       <c r="D12" t="str">
-        <v>q3,q4,q5</v>
+        <v>q1,q2,q3,q4,q5</v>
       </c>
       <c r="E12" t="str">
         <v>mean</v>
@@ -3174,24 +8404,1074 @@
         <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>课堂氛围、轻松感、被接纳、成就感（学生版情感维度）</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>学生感到被接纳、氛围轻松</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>感到紧张不放松、不被接纳</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B13" t="str">
+        <v>CS_S3D2</v>
+      </c>
+      <c r="C13" t="str">
+        <v>关系</v>
+      </c>
+      <c r="D13" t="str">
+        <v>q6,q7,q11,q12,q13,q14,q15,q24</v>
+      </c>
+      <c r="E13" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F13" t="str">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>集体荣誉、规则参与、同伴关系、师生交流（学生版关系维度）</v>
+      </c>
+      <c r="H13" t="str">
+        <v>归属感强，同伴与师生联结紧密</v>
+      </c>
+      <c r="I13" t="str">
+        <v>同伴联结薄弱，参与度低</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B14" t="str">
+        <v>CS_S3D3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>认知</v>
+      </c>
+      <c r="D14" t="str">
+        <v>q8,q9,q10,q17,q22</v>
+      </c>
+      <c r="E14" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F14" t="str">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>积极思考回答、订正、班级信心、主动交流（学生版认知维度）</v>
+      </c>
+      <c r="H14" t="str">
+        <v>学习投入与班级信心高</v>
+      </c>
+      <c r="I14" t="str">
+        <v>学习投入低，缺乏班级信心</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>CS_S3D4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>行为</v>
+      </c>
+      <c r="D15" t="str">
+        <v>q16,q18,q19,q20,q21</v>
+      </c>
+      <c r="E15" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F15" t="str">
+        <v>1</v>
+      </c>
+      <c r="G15" t="str">
+        <v>维护秩序、文明礼貌、同伴互助、回应批评（学生版行为维度）</v>
+      </c>
+      <c r="H15" t="str">
+        <v>行为自主规范，互助充分</v>
+      </c>
+      <c r="I15" t="str">
+        <v>行为依赖提醒，互助缺失</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CS_S3D5</v>
+      </c>
+      <c r="C16" t="str">
+        <v>环境</v>
+      </c>
+      <c r="D16" t="str">
+        <v>q23,q25</v>
+      </c>
+      <c r="E16" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F16" t="str">
+        <v>1</v>
+      </c>
+      <c r="G16" t="str">
+        <v>学习态度、求助行为（学生版环境维度·筛查层，不计入综合均值）</v>
+      </c>
+      <c r="H16" t="str">
+        <v>状态饱满、遇困求助</v>
+      </c>
+      <c r="I16" t="str">
+        <v>状态低迷、倾向放弃</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CS_S4D1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>情感</v>
+      </c>
+      <c r="D17" t="str">
+        <v>q1</v>
+      </c>
+      <c r="E17" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F17" t="str">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
+        <v>面部表情、整体情绪温度</v>
+      </c>
+      <c r="H17" t="str">
+        <v>表情放松、情绪温度高</v>
+      </c>
+      <c r="I17" t="str">
+        <v>表情紧绷、情绪温度低</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B18" t="str">
+        <v>CS_S4D2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>认知</v>
+      </c>
+      <c r="D18" t="str">
+        <v>q2</v>
+      </c>
+      <c r="E18" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F18" t="str">
+        <v>1</v>
+      </c>
+      <c r="G18" t="str">
+        <v>口头指代（我们班/这个班）、规则讨论频次</v>
+      </c>
+      <c r="H18" t="str">
+        <v>「我们班」占比高，认同高</v>
+      </c>
+      <c r="I18" t="str">
+        <v>「这个班」占比高，归属感弱</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CS_S4D3</v>
+      </c>
+      <c r="C19" t="str">
+        <v>行为</v>
+      </c>
+      <c r="D19" t="str">
+        <v>q3</v>
+      </c>
+      <c r="E19" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F19" t="str">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <v>课前状态、指令响应速度、自习纪律</v>
+      </c>
+      <c r="H19" t="str">
+        <v>课前状态稳、响应快、自习纪律好</v>
+      </c>
+      <c r="I19" t="str">
+        <v>需反复提醒、响应慢</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B20" t="str">
+        <v>CS_S4D4</v>
+      </c>
+      <c r="C20" t="str">
+        <v>关系</v>
+      </c>
+      <c r="D20" t="str">
+        <v>q4</v>
+      </c>
+      <c r="E20" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1</v>
+      </c>
+      <c r="G20" t="str">
+        <v>同伴互动（互助/冲突）、师生互动姿态</v>
+      </c>
+      <c r="H20" t="str">
+        <v>互助多、师生互动自然</v>
+      </c>
+      <c r="I20" t="str">
+        <v>冲突多、存在小圈子和落单者</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="B21" t="str">
+        <v>CS_S4D5</v>
+      </c>
+      <c r="C21" t="str">
+        <v>环境</v>
+      </c>
+      <c r="D21" t="str">
+        <v>q5</v>
+      </c>
+      <c r="E21" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F21" t="str">
+        <v>1</v>
+      </c>
+      <c r="G21" t="str">
+        <v>整洁度、绿植/布置（筛查层，不计入能量场综合均值）</v>
+      </c>
+      <c r="H21" t="str">
+        <v>整洁、布置有生机</v>
+      </c>
+      <c r="I21" t="str">
+        <v>杂乱、布置陈旧</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B22" t="str">
+        <v>CS_S5D1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>情感</v>
+      </c>
+      <c r="D22" t="str">
+        <v>q1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F22" t="str">
+        <v>1</v>
+      </c>
+      <c r="G22" t="str">
+        <v>1分=面无表情/趴桌比例&gt;30%；3分=部分学生主动参与；5分=集体自发的笑声、击掌</v>
+      </c>
+      <c r="H22" t="str">
+        <v>集体自发笑声、击掌</v>
+      </c>
+      <c r="I22" t="str">
+        <v>面无表情/趴桌比例&gt;30%</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B23" t="str">
+        <v>CS_S5D2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>认知</v>
+      </c>
+      <c r="D23" t="str">
+        <v>q2</v>
+      </c>
+      <c r="E23" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F23" t="str">
+        <v>1</v>
+      </c>
+      <c r="G23" t="str">
+        <v>1分=「这个班」频率高、外归因；3分=「我们班」与「这个班」并存；5分=「我们班」为主</v>
+      </c>
+      <c r="H23" t="str">
+        <v>「我们班」为主、主动为班级归因</v>
+      </c>
+      <c r="I23" t="str">
+        <v>「这个班」频率高、外归因</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B24" t="str">
+        <v>CS_S5D3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>行为</v>
+      </c>
+      <c r="D24" t="str">
+        <v>q3</v>
+      </c>
+      <c r="E24" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F24" t="str">
+        <v>1</v>
+      </c>
+      <c r="G24" t="str">
+        <v>1分=需反复提醒、抄作业现象多；3分=基本按时按质；5分=主动举手、主动完成</v>
+      </c>
+      <c r="H24" t="str">
+        <v>主动举手、主动完成</v>
+      </c>
+      <c r="I24" t="str">
+        <v>需反复提醒、抄作业现象多</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B25" t="str">
+        <v>CS_S5D4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>关系</v>
+      </c>
+      <c r="D25" t="str">
+        <v>q4</v>
+      </c>
+      <c r="E25" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F25" t="str">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <v>1分=独来独往比例高、冲突多；3分=小圈子明显但稳定；5分=课间合作游戏、主动找老师</v>
+      </c>
+      <c r="H25" t="str">
+        <v>课间合作游戏、主动找老师</v>
+      </c>
+      <c r="I25" t="str">
+        <v>独来独往比例高、冲突多</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_S5</v>
+      </c>
+      <c r="B26" t="str">
+        <v>CS_S5D5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>环境</v>
+      </c>
+      <c r="D26" t="str">
+        <v>q5</v>
+      </c>
+      <c r="E26" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F26" t="str">
+        <v>1</v>
+      </c>
+      <c r="G26" t="str">
+        <v>1分=桌椅乱、墙面陈旧、绿植枯萎；3分=基本整洁、布置常规；5分=教室有「家」的感觉（筛查层）</v>
+      </c>
+      <c r="H26" t="str">
+        <v>教室有「家」的感觉、学生主动维护</v>
+      </c>
+      <c r="I26" t="str">
+        <v>桌椅乱、墙面陈旧、绿植枯萎</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="B27" t="str">
+        <v>CS_S6D1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>风险等级</v>
+      </c>
+      <c r="D27" t="str">
+        <v>q1,q2,q3,q4,q5</v>
+      </c>
+      <c r="E27" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F27" t="str">
+        <v>1</v>
+      </c>
+      <c r="G27" t="str">
+        <v>A-E 五级点检命中（A安全危机/B高风险/C中度/D轻度/E健康观察），A/B 级须 24-48h 上报</v>
+      </c>
+      <c r="H27" t="str">
+        <v>命中高等级风险，需立即分级响应</v>
+      </c>
+      <c r="I27" t="str">
+        <v>仅命中 E 级健康观察</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B28" t="str">
+        <v>CS_S7D1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>通用</v>
+      </c>
+      <c r="D28" t="str">
+        <v>q1,q2,q3,q4,q5,q6,q7</v>
+      </c>
+      <c r="E28" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F28" t="str">
+        <v>1</v>
+      </c>
+      <c r="G28" t="str">
+        <v>通用绘画语言维度：画面布局/大小比例/透视空间/线条质量/阴影涂黑/省略缺失/附加物</v>
+      </c>
+      <c r="H28" t="str">
+        <v>命中多项红旗信号</v>
+      </c>
+      <c r="I28" t="str">
+        <v>无红旗信号</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B29" t="str">
+        <v>CS_S7D2</v>
+      </c>
+      <c r="C29" t="str">
+        <v>HTP·房</v>
+      </c>
+      <c r="D29" t="str">
+        <v>q8</v>
+      </c>
+      <c r="E29" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F29" t="str">
+        <v>1</v>
+      </c>
+      <c r="G29" t="str">
+        <v>房树人·房的门/窗：无门/重锁/铁栏；无窗</v>
+      </c>
+      <c r="H29" t="str">
+        <v>命中社交封闭信号</v>
+      </c>
+      <c r="I29" t="str">
+        <v>无红旗信号</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B30" t="str">
+        <v>CS_S7D3</v>
+      </c>
+      <c r="C30" t="str">
+        <v>HTP·树</v>
+      </c>
+      <c r="D30" t="str">
+        <v>q9</v>
+      </c>
+      <c r="E30" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F30" t="str">
+        <v>1</v>
+      </c>
+      <c r="G30" t="str">
+        <v>房树人·树的根/干：无根/根断；枯无皮/裂/虫洞/砍断</v>
+      </c>
+      <c r="H30" t="str">
+        <v>命中生命力受损信号</v>
+      </c>
+      <c r="I30" t="str">
+        <v>无红旗信号</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B31" t="str">
+        <v>CS_S7D4</v>
+      </c>
+      <c r="C31" t="str">
+        <v>HTP·人</v>
+      </c>
+      <c r="D31" t="str">
+        <v>q10</v>
+      </c>
+      <c r="E31" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F31" t="str">
+        <v>1</v>
+      </c>
+      <c r="G31" t="str">
+        <v>房树人·人的眼/臂/脸：眼被挖空；无臂；无脸</v>
+      </c>
+      <c r="H31" t="str">
+        <v>命中被监视感/行动力缺失信号</v>
+      </c>
+      <c r="I31" t="str">
+        <v>无红旗信号</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B32" t="str">
+        <v>CS_S7D5</v>
+      </c>
+      <c r="C32" t="str">
+        <v>雨中人</v>
+      </c>
+      <c r="D32" t="str">
+        <v>q11,q12,q13</v>
+      </c>
+      <c r="E32" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F32" t="str">
+        <v>1</v>
+      </c>
+      <c r="G32" t="str">
+        <v>雨中人：防护物/人物状态/积极资源</v>
+      </c>
+      <c r="H32" t="str">
+        <v>命中缺乏应对资源、被压垮信号</v>
+      </c>
+      <c r="I32" t="str">
+        <v>出现积极资源（保护性因素）</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="B33" t="str">
+        <v>CS_S7D6</v>
+      </c>
+      <c r="C33" t="str">
+        <v>树木画</v>
+      </c>
+      <c r="D33" t="str">
+        <v>q14,q15</v>
+      </c>
+      <c r="E33" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F33" t="str">
+        <v>1</v>
+      </c>
+      <c r="G33" t="str">
+        <v>树木画：树干纹理/气象附加</v>
+      </c>
+      <c r="H33" t="str">
+        <v>命中创伤印记/毁灭感信号</v>
+      </c>
+      <c r="I33" t="str">
+        <v>无红旗信号</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B34" t="str">
+        <v>CS_S8D1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>家庭背景</v>
+      </c>
+      <c r="D34" t="str">
+        <v>q1,q2,q3,q4,q5</v>
+      </c>
+      <c r="E34" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F34" t="str">
+        <v>1</v>
+      </c>
+      <c r="G34" t="str">
+        <v>家庭背景五问：依恋对象/照料回应/沟通开放度/创伤变化/依恋信号物</v>
+      </c>
+      <c r="H34" t="str">
+        <v>家庭依恋背景整体稳定</v>
+      </c>
+      <c r="I34" t="str">
+        <v>存在创伤/重大变化或回应模式不一致</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B35" t="str">
+        <v>CS_S8D2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>依恋类型</v>
+      </c>
+      <c r="D35" t="str">
+        <v>q6,q7,q8,q9</v>
+      </c>
+      <c r="E35" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F35" t="str">
+        <v>1</v>
+      </c>
+      <c r="G35" t="str">
+        <v>四类识别：安全型/A型回避/C型焦虑-矛盾/D型混乱</v>
+      </c>
+      <c r="H35" t="str">
+        <v>以安全型特征为主</v>
+      </c>
+      <c r="I35" t="str">
+        <v>出现回避/焦虑-矛盾/混乱型特征</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="B36" t="str">
+        <v>CS_S8D3</v>
+      </c>
+      <c r="C36" t="str">
+        <v>依恋观察</v>
+      </c>
+      <c r="D36" t="str">
+        <v>q10,q11,q12,q13,q14,q15,q16</v>
+      </c>
+      <c r="E36" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F36" t="str">
+        <v>1</v>
+      </c>
+      <c r="G36" t="str">
+        <v>快速观察清单 7 维度：情绪稳定性/社交连接/分离反应/求助行为/规则回应/任务投入/依恋信号物</v>
+      </c>
+      <c r="H36" t="str">
+        <v>各维度观察良好</v>
+      </c>
+      <c r="I36" t="str">
+        <v>多项观察异常</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="B37" t="str">
+        <v>CS_S9D1</v>
+      </c>
+      <c r="C37" t="str">
+        <v>个案类型</v>
+      </c>
+      <c r="D37" t="str">
+        <v>q1,q2,q3,q4</v>
+      </c>
+      <c r="E37" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1</v>
+      </c>
+      <c r="G37" t="str">
+        <v>能力×意愿四型：成功型/挫折型/对抗型/放弃型</v>
+      </c>
+      <c r="H37" t="str">
+        <v>命中需优先处理的类型</v>
+      </c>
+      <c r="I37" t="str">
+        <v>暂无明显个案类型</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B38" t="str">
+        <v>CS_S10D1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>情绪症状</v>
+      </c>
+      <c r="D38" t="str">
+        <v>q1</v>
+      </c>
+      <c r="E38" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F38" t="str">
+        <v>1</v>
+      </c>
+      <c r="G38" t="str">
+        <v>情绪低落、焦虑、恐惧、躯体不适（教师版评定）</v>
+      </c>
+      <c r="H38" t="str">
+        <v>达临床区间，需启动 B/C 级响应</v>
+      </c>
+      <c r="I38" t="str">
+        <v>正常区间</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B39" t="str">
+        <v>CS_S10D2</v>
+      </c>
+      <c r="C39" t="str">
+        <v>品行问题</v>
+      </c>
+      <c r="D39" t="str">
+        <v>q2</v>
+      </c>
+      <c r="E39" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F39" t="str">
+        <v>1</v>
+      </c>
+      <c r="G39" t="str">
+        <v>攻击、说谎、偷拿、违抗（结合日常观察）</v>
+      </c>
+      <c r="H39" t="str">
+        <v>异常，需关注</v>
+      </c>
+      <c r="I39" t="str">
+        <v>正常区间</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B40" t="str">
+        <v>CS_S10D3</v>
+      </c>
+      <c r="C40" t="str">
+        <v>多动注意</v>
+      </c>
+      <c r="D40" t="str">
+        <v>q3</v>
+      </c>
+      <c r="E40" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F40" t="str">
+        <v>1</v>
+      </c>
+      <c r="G40" t="str">
+        <v>坐不住、易分心、冲动（注意与环境干扰区分）</v>
+      </c>
+      <c r="H40" t="str">
+        <v>异常，需关注</v>
+      </c>
+      <c r="I40" t="str">
+        <v>正常区间</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B41" t="str">
+        <v>CS_S10D4</v>
+      </c>
+      <c r="C41" t="str">
+        <v>同伴交往</v>
+      </c>
+      <c r="D41" t="str">
+        <v>q4</v>
+      </c>
+      <c r="E41" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F41" t="str">
+        <v>1</v>
+      </c>
+      <c r="G41" t="str">
+        <v>孤独、被排挤、少朋友（关注社交回避）</v>
+      </c>
+      <c r="H41" t="str">
+        <v>异常，需关注</v>
+      </c>
+      <c r="I41" t="str">
+        <v>正常区间</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="B42" t="str">
+        <v>CS_S10D5</v>
+      </c>
+      <c r="C42" t="str">
+        <v>亲社会行为</v>
+      </c>
+      <c r="D42" t="str">
+        <v>q5</v>
+      </c>
+      <c r="E42" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F42" t="str">
+        <v>1</v>
+      </c>
+      <c r="G42" t="str">
+        <v>乐于助人、体谅他人（保护性因素）</v>
+      </c>
+      <c r="H42" t="str">
+        <v>保护性因素充足</v>
+      </c>
+      <c r="I42" t="str">
+        <v>亲社会行为不足</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K42"/>
   </ignoredErrors>
 </worksheet>
 </file>